--- a/docs/platform/p1-kit/boards/board-02-money.xlsx
+++ b/docs/platform/p1-kit/boards/board-02-money.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t xml:space="preserve">② 現在地ボード：家計・積立</t>
   </si>
@@ -31,7 +31,6 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -40,7 +39,6 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -50,63 +48,86 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">回、「記録」シートの黄色の欄に、その月の貯蓄額と月末の積立残高（評価額）を入れてください。金額はおおよそで構いません。</t>
+      <t xml:space="preserve">回、「記録」シートの「実績」に、月末の積立残高（評価額のおおよその額）を入れてください。</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">「計画」の残高は、初回の試算で決めた毎月の積立額と仮定の利回りで自動計算されます（予測・保証ではありません）。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">投資には元本割れのリスクがあります。銘柄や商品の選び方の助言はこのシートに含まれません。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">凡例</t>
-  </si>
-  <si>
-    <t xml:space="preserve">黄色のセル＝あなたが入力する欄（青字）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">白いセル＝自動計算（触らない）</t>
+    <t xml:space="preserve">入れると、現在地・目標までの進み具合と、期限までに目標に届くために必要な毎月の積立額が自動で計算され、残りの月の予定が作り直されます。</t>
   </si>
   <si>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">利回りは仮定です（予測・保証ではありません）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">1</t>
+      <t xml:space="preserve">0%</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">行目の数字は記入例（架空）です。上書きしてお使いください。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">このシートは目安を可視化するもので、結果を保証するものではありません。氏名・口座番号・</t>
+      <t xml:space="preserve">やマイナスでも試してください。税金（課税口座は利益に原則</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20.315%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）は含みません。銘柄や商品の選び方の助言は含みません。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">凡例</t>
+  </si>
+  <si>
+    <t xml:space="preserve">黄色のセル（青字）＝あなたが入力する欄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">緑のセル＝自動で計算される「現在地」と「これからの予定」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">その他の白いセル＝自動計算（触らない）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">入っている数字は架空の記入例です。上書きしてお使いください。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">このシートは、入力した数字から機械的に計算した目安です。結果を保証するものではありません。氏名・口座番号・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <rFont val="Arial"/>
         <family val="0"/>
         <charset val="1"/>
@@ -116,18 +137,23 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color theme="1"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">・パスワードなどは書かないでください。</t>
+      <t xml:space="preserve">・パスワード・学校名などは書かないでください。</t>
     </r>
   </si>
   <si>
     <t xml:space="preserve">前提（仮定条件）</t>
   </si>
   <si>
-    <t xml:space="preserve">毎月の積立額（円）</t>
+    <t xml:space="preserve">最初の積立残高（円）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">目標の積立残高（円）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">期限までの月数</t>
   </si>
   <si>
     <t xml:space="preserve">仮定の利回り（年）</t>
@@ -136,386 +162,74 @@
     <t xml:space="preserve">運用手数料（年）</t>
   </si>
   <si>
-    <t xml:space="preserve">毎月の貯蓄目標（円）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">※ 利回りは仮定です。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">0%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">やマイナスのケースも試してください。税金（課税口座は利益に原則</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20.315%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）は含みません。</t>
-    </r>
+    <t xml:space="preserve">月あたりの実質利回り（自動）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">当初の計画の毎月の積立額（自動・円）</t>
   </si>
   <si>
     <t xml:space="preserve">月</t>
   </si>
   <si>
-    <t xml:space="preserve">計画の積立残高（円・仮定）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">実績の積立残高（円）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">差（実績−計画）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">積立元本（円）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">その月の貯蓄額（円）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">貯蓄目標との差（円）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">か月目</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">か月目</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">か月目</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">か月目</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">か月目</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">か月目</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">か月目</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">か月目</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">か月目</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">か月目</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">11</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">か月目</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">か月目</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">※ 実績・貯蓄額の数字は架空の記入例です。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">現在地ボード：家計・積立（仮定条件にもとづく）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">最新の積立残高（円）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">同じ月の計画残高（円）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">計画との差（円）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">か月後の計画残高（円）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">貯蓄目標を達成した月の数</t>
-  </si>
-  <si>
-    <t xml:space="preserve">記録した月の数</t>
-  </si>
-  <si>
-    <t xml:space="preserve">※ 計画残高は仮定の利回りでの試算で、予測・保証ではありません。</t>
+    <t xml:space="preserve">当初の計画（円・仮定）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">実績（円）※入力</t>
+  </si>
+  <si>
+    <t xml:space="preserve">更新後の予定（円・仮定）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">※ 入力するのは「実績」の列だけです。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">現在地ボード：家計・積立（仮定条件にもとづく試算）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">現在地</t>
+  </si>
+  <si>
+    <t xml:space="preserve">記録した月数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">現在の積立残高（円）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">目標（円）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">目標までの進み具合</t>
+  </si>
+  <si>
+    <t xml:space="preserve">当初の計画と比べて</t>
+  </si>
+  <si>
+    <t xml:space="preserve">残りの月数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">目標に届くために必要な毎月の積立額（更新後・円）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">当初の計画の毎月の積立額（円）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">当初の積立額を続けた場合の期限時点の残高（円）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">※ 仮定の利回りによる機械的な計算で、予測・保証ではありません。投資には元本割れのリスクがあります。税金は含みません。</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="#,##0"/>
-    <numFmt numFmtId="167" formatCode="#,##0;\-#,##0;0"/>
-    <numFmt numFmtId="168" formatCode="0"/>
+    <numFmt numFmtId="165" formatCode="#,##0"/>
+    <numFmt numFmtId="166" formatCode="0"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="0.000%"/>
+    <numFmt numFmtId="169" formatCode="0%"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -548,13 +262,11 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -579,6 +291,7 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
       <sz val="11"/>
       <name val="Arial"/>
       <family val="0"/>
@@ -605,7 +318,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -615,13 +328,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFE2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F0D9"/>
+        <bgColor rgb="FFDDE6F5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDE6F5"/>
-        <bgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -674,7 +393,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -695,23 +414,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -719,19 +430,35 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -780,7 +507,7 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFE2F0D9"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -788,7 +515,7 @@
       <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FF98B855"/>
       <rgbColor rgb="FFFFCC00"/>
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
@@ -833,7 +560,7 @@
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>積立残高：計画（仮定）と実績</a:t>
+              <a:t>当初の計画・実績・更新後の予定（仮定）</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -860,7 +587,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>計画の積立残高（円・仮定）</c:v>
+                  <c:v>当初の計画（円・仮定）</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -906,89 +633,197 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>記録!$A$2:$A$13</c:f>
+              <c:f>記録!$A$2:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="12"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
-                  <c:v>1か月目</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2か月目</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3か月目</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4か月目</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5か月目</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6か月目</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7か月目</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8か月目</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9か月目</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10か月目</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>11か月目</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>12か月目</c:v>
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>記録!$B$2:$B$13</c:f>
+              <c:f>記録!$B$2:$B$31</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
-                  <c:v>30000</c:v>
+                  <c:v>32179.84338037</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>60072.5</c:v>
+                  <c:v>64437.4547155767</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>90217.6752083333</c:v>
+                  <c:v>96773.0219448413</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>120435.701256753</c:v>
+                  <c:v>129186.733461579</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>150726.754201457</c:v>
+                  <c:v>161678.778114479</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>181091.010524111</c:v>
+                  <c:v>194249.345208628</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>211528.647132877</c:v>
+                  <c:v>226898.624506586</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>242039.841363449</c:v>
+                  <c:v>259626.806229513</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>272624.770980077</c:v>
+                  <c:v>292434.081058269</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>303283.614176612</c:v>
+                  <c:v>325320.640134532</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>334016.549577539</c:v>
+                  <c:v>358286.675061893</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>364823.756239018</c:v>
+                  <c:v>391332.377906997</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>424457.941200641</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>457663.557938913</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>490949.421584303</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>524315.726066834</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>557762.6657852</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>591290.435607884</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>624899.230874306</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>658589.247395956</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>692360.681457534</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>726213.729818092</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>760148.589712189</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>794165.45885103</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>828264.535423623</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>862446.018097934</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>896710.106022042</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>931056.998825299</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>965486.896619496</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1000000.00000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1004,7 +839,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>実績の積立残高（円）</c:v>
+                  <c:v>実績（円）※入力</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1050,62 +885,359 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>記録!$A$2:$A$13</c:f>
+              <c:f>記録!$A$2:$A$31</c:f>
               <c:strCache>
-                <c:ptCount val="12"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
-                  <c:v>1か月目</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2か月目</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3か月目</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4か月目</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5か月目</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6か月目</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>7か月目</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>8か月目</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>9か月目</c:v>
+                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>10か月目</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>11か月目</c:v>
+                  <c:v>11</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>12か月目</c:v>
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>記録!$C$2:$C$13</c:f>
+              <c:f>記録!$C$2:$C$31</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="12"/>
+                <c:ptCount val="30"/>
                 <c:pt idx="0">
-                  <c:v>30000</c:v>
+                  <c:v>30500</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>61000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>90500</c:v>
+                  <c:v>90000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>118000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>記録!D1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>更新後の予定（円・仮定）</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="98b855"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="98b855"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>記録!$A$2:$A$31</c:f>
+              <c:strCache>
+                <c:ptCount val="30"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>記録!$D$2:$D$31</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="30"/>
+                <c:pt idx="4">
+                  <c:v>150909.447392526</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>183898.425949584</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>216967.127871486</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>250115.745823035</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>283344.472934632</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>316653.502803418</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>350043.029494386</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>383513.247541523</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>417064.351948939</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>450696.53819201</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>484410.002218498</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>518204.940449719</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>552081.549781664</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>586040.027586163</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>620080.571712022</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>654203.380486184</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>688408.652714886</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>722696.587684805</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>757067.385164236</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>791521.245404242</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>826058.369139829</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>860678.957591108</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>895383.212464479</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>930171.335953793</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>965043.530741541</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1000000.00000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1120,17 +1252,17 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="49985257"/>
-        <c:axId val="90247127"/>
+        <c:axId val="61893748"/>
+        <c:axId val="11597768"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="49985257"/>
+        <c:axId val="61893748"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1156,7 +1288,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90247127"/>
+        <c:crossAx val="11597768"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1164,7 +1296,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="90247127"/>
+        <c:axId val="11597768"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1240,7 +1372,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49985257"/>
+        <c:crossAx val="61893748"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1302,10 +1434,10 @@
       <xdr:rowOff>160560</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>364680</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>155520</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>473040</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>90000</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1313,8 +1445,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3853800" y="380880"/>
-        <a:ext cx="6479640" cy="2879640"/>
+        <a:off x="5263560" y="380880"/>
+        <a:ext cx="7199640" cy="3239640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1507,10 +1639,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="100"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="110"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1528,7 +1660,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -1544,18 +1676,23 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1574,53 +1711,74 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="6" t="n">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
         <v>11</v>
       </c>
+      <c r="B2" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>12</v>
+      </c>
       <c r="B3" s="7" t="n">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="8" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="9" t="n">
         <v>0.03</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="7" t="n">
+    <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="9" t="n">
         <v>0.001</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>20000</v>
-      </c>
-    </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>14</v>
+      <c r="A7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="10" t="n">
+        <f aca="false">(B5-B6)/12</f>
+        <v>0.00241666666666667</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="11" t="n">
+        <f aca="false">IF(B7=0,(B3-B2)/B4,PMT(B7,B4,B2,-B3))</f>
+        <v>32179.8433803691</v>
       </c>
     </row>
   </sheetData>
@@ -1639,331 +1797,460 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A2,FV(前提!$B$7,A2,-前提!$B$8,-前提!$B$2))</f>
+        <v>32179.84338037</v>
+      </c>
+      <c r="C2" s="7" t="n">
+        <v>30500</v>
+      </c>
+      <c r="D2" s="11" t="str">
+        <f aca="false">IF(OR(ボード!$B$4="",A2&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A2-ボード!$B$4),FV(前提!$B$7,A2-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A3,FV(前提!$B$7,A3,-前提!$B$8,-前提!$B$2))</f>
+        <v>64437.4547155767</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>61000</v>
+      </c>
+      <c r="D3" s="11" t="str">
+        <f aca="false">IF(OR(ボード!$B$4="",A3&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A3-ボード!$B$4),FV(前提!$B$7,A3-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A4,FV(前提!$B$7,A4,-前提!$B$8,-前提!$B$2))</f>
+        <v>96773.0219448413</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>90000</v>
+      </c>
+      <c r="D4" s="11" t="str">
+        <f aca="false">IF(OR(ボード!$B$4="",A4&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A4-ボード!$B$4),FV(前提!$B$7,A4-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A5,FV(前提!$B$7,A5,-前提!$B$8,-前提!$B$2))</f>
+        <v>129186.733461579</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>118000</v>
+      </c>
+      <c r="D5" s="11" t="str">
+        <f aca="false">IF(OR(ボード!$B$4="",A5&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A5-ボード!$B$4),FV(前提!$B$7,A5-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A6,FV(前提!$B$7,A6,-前提!$B$8,-前提!$B$2))</f>
+        <v>161678.778114479</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="11" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A6&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A6-ボード!$B$4),FV(前提!$B$7,A6-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <v>150909.447392526</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A7,FV(前提!$B$7,A7,-前提!$B$8,-前提!$B$2))</f>
+        <v>194249.345208628</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="11" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A7&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A7-ボード!$B$4),FV(前提!$B$7,A7-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <v>183898.425949584</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="11" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A8,FV(前提!$B$7,A8,-前提!$B$8,-前提!$B$2))</f>
+        <v>226898.624506586</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="11" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A8&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A8-ボード!$B$4),FV(前提!$B$7,A8-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <v>216967.127871486</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A9,FV(前提!$B$7,A9,-前提!$B$8,-前提!$B$2))</f>
+        <v>259626.806229513</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="11" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A9&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A9-ボード!$B$4),FV(前提!$B$7,A9-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <v>250115.745823035</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="11" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A10,FV(前提!$B$7,A10,-前提!$B$8,-前提!$B$2))</f>
+        <v>292434.081058269</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="11" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A10&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A10-ボード!$B$4),FV(前提!$B$7,A10-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <v>283344.472934632</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="11" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A11,FV(前提!$B$7,A11,-前提!$B$8,-前提!$B$2))</f>
+        <v>325320.640134532</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="11" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A11&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A11-ボード!$B$4),FV(前提!$B$7,A11-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <v>316653.502803418</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="11" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A12,FV(前提!$B$7,A12,-前提!$B$8,-前提!$B$2))</f>
+        <v>358286.675061893</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="11" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A12&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A12-ボード!$B$4),FV(前提!$B$7,A12-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <v>350043.029494386</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="11" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A13,FV(前提!$B$7,A13,-前提!$B$8,-前提!$B$2))</f>
+        <v>391332.377906997</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="11" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A13&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A13-ボード!$B$4),FV(前提!$B$7,A13-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <v>383513.247541523</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="13" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="11" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A14,FV(前提!$B$7,A14,-前提!$B$8,-前提!$B$2))</f>
+        <v>424457.941200641</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="11" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A14&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A14-ボード!$B$4),FV(前提!$B$7,A14-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <v>417064.351948939</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="11" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A15,FV(前提!$B$7,A15,-前提!$B$8,-前提!$B$2))</f>
+        <v>457663.557938913</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="11" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A15&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A15-ボード!$B$4),FV(前提!$B$7,A15-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <v>450696.53819201</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="13" t="n">
         <v>15</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B16" s="11" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A16,FV(前提!$B$7,A16,-前提!$B$8,-前提!$B$2))</f>
+        <v>490949.421584303</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="11" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A16&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A16-ボード!$B$4),FV(前提!$B$7,A16-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <v>484410.002218498</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="13" t="n">
         <v>16</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="B17" s="11" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A17,FV(前提!$B$7,A17,-前提!$B$8,-前提!$B$2))</f>
+        <v>524315.726066834</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="11" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A17&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A17-ボード!$B$4),FV(前提!$B$7,A17-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <v>518204.940449719</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="13" t="n">
         <v>17</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="B18" s="11" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A18,FV(前提!$B$7,A18,-前提!$B$8,-前提!$B$2))</f>
+        <v>557762.6657852</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="11" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A18&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A18-ボード!$B$4),FV(前提!$B$7,A18-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <v>552081.549781664</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="13" t="n">
         <v>18</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="B19" s="11" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A19,FV(前提!$B$7,A19,-前提!$B$8,-前提!$B$2))</f>
+        <v>591290.435607884</v>
+      </c>
+      <c r="C19" s="7"/>
+      <c r="D19" s="11" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A19&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A19-ボード!$B$4),FV(前提!$B$7,A19-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <v>586040.027586163</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="13" t="n">
         <v>19</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="B20" s="11" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A20,FV(前提!$B$7,A20,-前提!$B$8,-前提!$B$2))</f>
+        <v>624899.230874306</v>
+      </c>
+      <c r="C20" s="7"/>
+      <c r="D20" s="11" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A20&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A20-ボード!$B$4),FV(前提!$B$7,A20-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <v>620080.571712022</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="B21" s="11" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A21,FV(前提!$B$7,A21,-前提!$B$8,-前提!$B$2))</f>
+        <v>658589.247395956</v>
+      </c>
+      <c r="C21" s="7"/>
+      <c r="D21" s="11" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A21&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A21-ボード!$B$4),FV(前提!$B$7,A21-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <v>654203.380486184</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="13" t="n">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
+      <c r="B22" s="11" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A22,FV(前提!$B$7,A22,-前提!$B$8,-前提!$B$2))</f>
+        <v>692360.681457534</v>
+      </c>
+      <c r="C22" s="7"/>
+      <c r="D22" s="11" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A22&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A22-ボード!$B$4),FV(前提!$B$7,A22-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <v>688408.652714886</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="13" t="n">
         <v>22</v>
       </c>
-      <c r="B2" s="9" t="n">
-        <f aca="false">前提!$B$2</f>
-        <v>30000</v>
-      </c>
-      <c r="C2" s="10" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D2" s="11" t="n">
-        <f aca="false">IF(C2="","",C2-B2)</f>
-        <v>0</v>
-      </c>
-      <c r="E2" s="9" t="n">
-        <f aca="false">前提!$B$2*1</f>
-        <v>30000</v>
-      </c>
-      <c r="F2" s="10" t="n">
-        <v>22000</v>
-      </c>
-      <c r="G2" s="11" t="n">
-        <f aca="false">IF(F2="","",F2-前提!$B$5)</f>
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+      <c r="B23" s="11" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A23,FV(前提!$B$7,A23,-前提!$B$8,-前提!$B$2))</f>
+        <v>726213.729818092</v>
+      </c>
+      <c r="C23" s="7"/>
+      <c r="D23" s="11" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A23&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A23-ボード!$B$4),FV(前提!$B$7,A23-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <v>722696.587684805</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="13" t="n">
         <v>23</v>
       </c>
-      <c r="B3" s="9" t="n">
-        <f aca="false">B2*(1+(前提!$B$3-前提!$B$4)/12)+前提!$B$2</f>
-        <v>60072.5</v>
-      </c>
-      <c r="C3" s="10" t="n">
-        <v>61000</v>
-      </c>
-      <c r="D3" s="11" t="n">
-        <f aca="false">IF(C3="","",C3-B3)</f>
-        <v>927.5</v>
-      </c>
-      <c r="E3" s="9" t="n">
-        <f aca="false">前提!$B$2*2</f>
-        <v>60000</v>
-      </c>
-      <c r="F3" s="10" t="n">
-        <v>18000</v>
-      </c>
-      <c r="G3" s="11" t="n">
-        <f aca="false">IF(F3="","",F3-前提!$B$5)</f>
-        <v>-2000</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+      <c r="B24" s="11" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A24,FV(前提!$B$7,A24,-前提!$B$8,-前提!$B$2))</f>
+        <v>760148.589712189</v>
+      </c>
+      <c r="C24" s="7"/>
+      <c r="D24" s="11" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A24&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A24-ボード!$B$4),FV(前提!$B$7,A24-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <v>757067.385164236</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="13" t="n">
         <v>24</v>
       </c>
-      <c r="B4" s="9" t="n">
-        <f aca="false">B3*(1+(前提!$B$3-前提!$B$4)/12)+前提!$B$2</f>
-        <v>90217.6752083333</v>
-      </c>
-      <c r="C4" s="10" t="n">
-        <v>90500</v>
-      </c>
-      <c r="D4" s="11" t="n">
-        <f aca="false">IF(C4="","",C4-B4)</f>
-        <v>282.324791666673</v>
-      </c>
-      <c r="E4" s="9" t="n">
-        <f aca="false">前提!$B$2*3</f>
-        <v>90000</v>
-      </c>
-      <c r="F4" s="10" t="n">
-        <v>25000</v>
-      </c>
-      <c r="G4" s="11" t="n">
-        <f aca="false">IF(F4="","",F4-前提!$B$5)</f>
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+      <c r="B25" s="11" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A25,FV(前提!$B$7,A25,-前提!$B$8,-前提!$B$2))</f>
+        <v>794165.45885103</v>
+      </c>
+      <c r="C25" s="7"/>
+      <c r="D25" s="11" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A25&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A25-ボード!$B$4),FV(前提!$B$7,A25-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <v>791521.245404242</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="13" t="n">
         <v>25</v>
       </c>
-      <c r="B5" s="9" t="n">
-        <f aca="false">B4*(1+(前提!$B$3-前提!$B$4)/12)+前提!$B$2</f>
-        <v>120435.701256753</v>
-      </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="11" t="str">
-        <f aca="false">IF(C5="","",C5-B5)</f>
-        <v/>
-      </c>
-      <c r="E5" s="9" t="n">
-        <f aca="false">前提!$B$2*4</f>
-        <v>120000</v>
-      </c>
-      <c r="F5" s="10"/>
-      <c r="G5" s="11" t="str">
-        <f aca="false">IF(F5="","",F5-前提!$B$5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+      <c r="B26" s="11" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A26,FV(前提!$B$7,A26,-前提!$B$8,-前提!$B$2))</f>
+        <v>828264.535423623</v>
+      </c>
+      <c r="C26" s="7"/>
+      <c r="D26" s="11" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A26&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A26-ボード!$B$4),FV(前提!$B$7,A26-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <v>826058.369139829</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="13" t="n">
         <v>26</v>
       </c>
-      <c r="B6" s="9" t="n">
-        <f aca="false">B5*(1+(前提!$B$3-前提!$B$4)/12)+前提!$B$2</f>
-        <v>150726.754201457</v>
-      </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="11" t="str">
-        <f aca="false">IF(C6="","",C6-B6)</f>
-        <v/>
-      </c>
-      <c r="E6" s="9" t="n">
-        <f aca="false">前提!$B$2*5</f>
-        <v>150000</v>
-      </c>
-      <c r="F6" s="10"/>
-      <c r="G6" s="11" t="str">
-        <f aca="false">IF(F6="","",F6-前提!$B$5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
+      <c r="B27" s="11" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A27,FV(前提!$B$7,A27,-前提!$B$8,-前提!$B$2))</f>
+        <v>862446.018097934</v>
+      </c>
+      <c r="C27" s="7"/>
+      <c r="D27" s="11" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A27&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A27-ボード!$B$4),FV(前提!$B$7,A27-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <v>860678.957591108</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="13" t="n">
         <v>27</v>
       </c>
-      <c r="B7" s="9" t="n">
-        <f aca="false">B6*(1+(前提!$B$3-前提!$B$4)/12)+前提!$B$2</f>
-        <v>181091.010524111</v>
-      </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="11" t="str">
-        <f aca="false">IF(C7="","",C7-B7)</f>
-        <v/>
-      </c>
-      <c r="E7" s="9" t="n">
-        <f aca="false">前提!$B$2*6</f>
-        <v>180000</v>
-      </c>
-      <c r="F7" s="10"/>
-      <c r="G7" s="11" t="str">
-        <f aca="false">IF(F7="","",F7-前提!$B$5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+      <c r="B28" s="11" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A28,FV(前提!$B$7,A28,-前提!$B$8,-前提!$B$2))</f>
+        <v>896710.106022042</v>
+      </c>
+      <c r="C28" s="7"/>
+      <c r="D28" s="11" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A28&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A28-ボード!$B$4),FV(前提!$B$7,A28-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <v>895383.212464479</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="13" t="n">
         <v>28</v>
       </c>
-      <c r="B8" s="9" t="n">
-        <f aca="false">B7*(1+(前提!$B$3-前提!$B$4)/12)+前提!$B$2</f>
-        <v>211528.647132877</v>
-      </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11" t="str">
-        <f aca="false">IF(C8="","",C8-B8)</f>
-        <v/>
-      </c>
-      <c r="E8" s="9" t="n">
-        <f aca="false">前提!$B$2*7</f>
-        <v>210000</v>
-      </c>
-      <c r="F8" s="10"/>
-      <c r="G8" s="11" t="str">
-        <f aca="false">IF(F8="","",F8-前提!$B$5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
+      <c r="B29" s="11" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A29,FV(前提!$B$7,A29,-前提!$B$8,-前提!$B$2))</f>
+        <v>931056.998825299</v>
+      </c>
+      <c r="C29" s="7"/>
+      <c r="D29" s="11" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A29&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A29-ボード!$B$4),FV(前提!$B$7,A29-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <v>930171.335953793</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="13" t="n">
         <v>29</v>
       </c>
-      <c r="B9" s="9" t="n">
-        <f aca="false">B8*(1+(前提!$B$3-前提!$B$4)/12)+前提!$B$2</f>
-        <v>242039.841363449</v>
-      </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="11" t="str">
-        <f aca="false">IF(C9="","",C9-B9)</f>
-        <v/>
-      </c>
-      <c r="E9" s="9" t="n">
-        <f aca="false">前提!$B$2*8</f>
-        <v>240000</v>
-      </c>
-      <c r="F9" s="10"/>
-      <c r="G9" s="11" t="str">
-        <f aca="false">IF(F9="","",F9-前提!$B$5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
+      <c r="B30" s="11" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A30,FV(前提!$B$7,A30,-前提!$B$8,-前提!$B$2))</f>
+        <v>965486.896619496</v>
+      </c>
+      <c r="C30" s="7"/>
+      <c r="D30" s="11" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A30&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A30-ボード!$B$4),FV(前提!$B$7,A30-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <v>965043.530741541</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="B10" s="9" t="n">
-        <f aca="false">B9*(1+(前提!$B$3-前提!$B$4)/12)+前提!$B$2</f>
-        <v>272624.770980077</v>
-      </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="11" t="str">
-        <f aca="false">IF(C10="","",C10-B10)</f>
-        <v/>
-      </c>
-      <c r="E10" s="9" t="n">
-        <f aca="false">前提!$B$2*9</f>
-        <v>270000</v>
-      </c>
-      <c r="F10" s="10"/>
-      <c r="G10" s="11" t="str">
-        <f aca="false">IF(F10="","",F10-前提!$B$5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="9" t="n">
-        <f aca="false">B10*(1+(前提!$B$3-前提!$B$4)/12)+前提!$B$2</f>
-        <v>303283.614176612</v>
-      </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="11" t="str">
-        <f aca="false">IF(C11="","",C11-B11)</f>
-        <v/>
-      </c>
-      <c r="E11" s="9" t="n">
-        <f aca="false">前提!$B$2*10</f>
-        <v>300000</v>
-      </c>
-      <c r="F11" s="10"/>
-      <c r="G11" s="11" t="str">
-        <f aca="false">IF(F11="","",F11-前提!$B$5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="9" t="n">
-        <f aca="false">B11*(1+(前提!$B$3-前提!$B$4)/12)+前提!$B$2</f>
-        <v>334016.549577539</v>
-      </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="11" t="str">
-        <f aca="false">IF(C12="","",C12-B12)</f>
-        <v/>
-      </c>
-      <c r="E12" s="9" t="n">
-        <f aca="false">前提!$B$2*11</f>
-        <v>330000</v>
-      </c>
-      <c r="F12" s="10"/>
-      <c r="G12" s="11" t="str">
-        <f aca="false">IF(F12="","",F12-前提!$B$5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="9" t="n">
-        <f aca="false">B12*(1+(前提!$B$3-前提!$B$4)/12)+前提!$B$2</f>
-        <v>364823.756239018</v>
-      </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="11" t="str">
-        <f aca="false">IF(C13="","",C13-B13)</f>
-        <v/>
-      </c>
-      <c r="E13" s="9" t="n">
-        <f aca="false">前提!$B$2*12</f>
-        <v>360000</v>
-      </c>
-      <c r="F13" s="10"/>
-      <c r="G13" s="11" t="str">
-        <f aca="false">IF(F13="","",F13-前提!$B$5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
-        <v>34</v>
+      <c r="B31" s="11" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A31,FV(前提!$B$7,A31,-前提!$B$8,-前提!$B$2))</f>
+        <v>1000000.00000003</v>
+      </c>
+      <c r="C31" s="7"/>
+      <c r="D31" s="11" t="n">
+        <f aca="false">IF(OR(ボード!$B$4="",A31&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A31-ボード!$B$4),FV(前提!$B$7,A31-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <v>1000000.00000003</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1982,75 +2269,107 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="9" t="n">
-        <f aca="false">IFERROR(LOOKUP(2,1/(記録!C2:C13&lt;&gt;""),記録!C2:C13),"")</f>
-        <v>90500</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="9" t="n">
-        <f aca="false">IFERROR(INDEX(記録!B2:B13,COUNT(記録!C2:C13)),"")</f>
-        <v>90217.6752083333</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="11" t="n">
-        <f aca="false">IFERROR(B3-B4,"")</f>
-        <v>282.324791666673</v>
+      <c r="A3" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="13" t="n">
+        <f aca="false">IF(COUNT(記録!C2:C31)=0,"",COUNT(記録!C2:C31))</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="14" t="n">
+        <f aca="false">IF(B4="","",LOOKUP(2,1/(記録!C2:C31&lt;&gt;""),記録!C2:C31))</f>
+        <v>118000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="9" t="n">
-        <f aca="false">記録!B13</f>
-        <v>364823.756239018</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="14" t="n">
-        <f aca="false">COUNTIFS(記録!G2:G13,"&gt;=0")</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="14" t="n">
-        <f aca="false">COUNT(記録!F2:F13)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>42</v>
+      <c r="A6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="11" t="n">
+        <f aca="false">前提!B3</f>
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="15" t="n">
+        <f aca="false">IFERROR((B5-前提!B2)/(前提!B3-前提!B2),"")</f>
+        <v>0.118</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="16" t="str">
+        <f aca="false">IF(B4="","",IF(B5&gt;=INDEX(記録!B2:B31,B4),"計画どおり、または先行","計画より遅れ"))</f>
+        <v>計画より遅れ</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="13" t="n">
+        <f aca="false">IF(B4="","",前提!B4-B4)</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="14" t="n">
+        <f aca="false">IFERROR(IF(B9&lt;=0,"",IF(B5&gt;=前提!B3,0,IF(前提!B7=0,(前提!B3-B5)/B9,PMT(前提!B7,B9,B5,-前提!B3)))),"")</f>
+        <v>32624.2807258581</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="11" t="n">
+        <f aca="false">前提!B8</f>
+        <v>32179.8433803691</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="14" t="n">
+        <f aca="false">IFERROR(IF(B9&lt;=0,B5,IF(前提!B7=0,B5+前提!B8*B9,FV(前提!B7,B9,-前提!B8,-B5))),"")</f>
+        <v>988088.717077351</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/docs/platform/p1-kit/boards/board-02-money.xlsx
+++ b/docs/platform/p1-kit/boards/board-02-money.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t xml:space="preserve">② 現在地ボード：家計・積立</t>
   </si>
@@ -189,7 +189,7 @@
     <t xml:space="preserve">現在地</t>
   </si>
   <si>
-    <t xml:space="preserve">記録した月数</t>
+    <t xml:space="preserve">最後に実績を入れた月</t>
   </si>
   <si>
     <t xml:space="preserve">現在の積立残高（円）</t>
@@ -213,10 +213,57 @@
     <t xml:space="preserve">当初の計画の毎月の積立額（円）</t>
   </si>
   <si>
-    <t xml:space="preserve">当初の積立額を続けた場合の期限時点の残高（円）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">※ 仮定の利回りによる機械的な計算で、予測・保証ではありません。投資には元本割れのリスクがあります。税金は含みません。</t>
+    <t xml:space="preserve">当初の積立額を続けた場合の期限時点の残高（円・仮定）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">入力のチェック</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">計算の前提：月あたりの利回り＝（年の利回り−年の運用手数料）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">。最初の残高は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月目の初めにあり、毎月の積立は月末に入る。複利は月ごと。税金・物価上昇は含まない。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">※ 仮定の利回りによる機械的な計算で、予測・保証ではありません。投資には元本割れのリスクがあります。</t>
   </si>
 </sst>
 </file>
@@ -393,7 +440,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -459,6 +506,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1252,11 +1303,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="61893748"/>
-        <c:axId val="11597768"/>
+        <c:axId val="82735445"/>
+        <c:axId val="1061964"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="61893748"/>
+        <c:axId val="82735445"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1288,7 +1339,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11597768"/>
+        <c:crossAx val="1061964"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1296,7 +1347,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="11597768"/>
+        <c:axId val="1061964"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1372,7 +1423,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61893748"/>
+        <c:crossAx val="82735445"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1437,7 +1488,7 @@
       <xdr:col>14</xdr:col>
       <xdr:colOff>473040</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>90000</xdr:rowOff>
+      <xdr:rowOff>35280</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1782,6 +1833,12 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" error="0以上の数字を入れてください" errorStyle="stop" errorTitle="入力の確認" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B2:B4" type="decimal">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1832,7 +1889,7 @@
         <v>30500</v>
       </c>
       <c r="D2" s="11" t="str">
-        <f aca="false">IF(OR(ボード!$B$4="",A2&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A2-ボード!$B$4),FV(前提!$B$7,A2-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A2&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A2-ボード!$B$4),FV(前提!$B$7,A2-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v/>
       </c>
     </row>
@@ -1848,7 +1905,7 @@
         <v>61000</v>
       </c>
       <c r="D3" s="11" t="str">
-        <f aca="false">IF(OR(ボード!$B$4="",A3&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A3-ボード!$B$4),FV(前提!$B$7,A3-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A3&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A3-ボード!$B$4),FV(前提!$B$7,A3-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v/>
       </c>
     </row>
@@ -1864,7 +1921,7 @@
         <v>90000</v>
       </c>
       <c r="D4" s="11" t="str">
-        <f aca="false">IF(OR(ボード!$B$4="",A4&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A4-ボード!$B$4),FV(前提!$B$7,A4-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A4&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A4-ボード!$B$4),FV(前提!$B$7,A4-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v/>
       </c>
     </row>
@@ -1880,7 +1937,7 @@
         <v>118000</v>
       </c>
       <c r="D5" s="11" t="str">
-        <f aca="false">IF(OR(ボード!$B$4="",A5&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A5-ボード!$B$4),FV(前提!$B$7,A5-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A5&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A5-ボード!$B$4),FV(前提!$B$7,A5-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v/>
       </c>
     </row>
@@ -1894,7 +1951,7 @@
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="11" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A6&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A6-ボード!$B$4),FV(前提!$B$7,A6-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A6&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A6-ボード!$B$4),FV(前提!$B$7,A6-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>150909.447392526</v>
       </c>
     </row>
@@ -1908,7 +1965,7 @@
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="11" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A7&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A7-ボード!$B$4),FV(前提!$B$7,A7-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A7&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A7-ボード!$B$4),FV(前提!$B$7,A7-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>183898.425949584</v>
       </c>
     </row>
@@ -1922,7 +1979,7 @@
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="11" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A8&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A8-ボード!$B$4),FV(前提!$B$7,A8-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A8&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A8-ボード!$B$4),FV(前提!$B$7,A8-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>216967.127871486</v>
       </c>
     </row>
@@ -1936,7 +1993,7 @@
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="11" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A9&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A9-ボード!$B$4),FV(前提!$B$7,A9-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A9&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A9-ボード!$B$4),FV(前提!$B$7,A9-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>250115.745823035</v>
       </c>
     </row>
@@ -1950,7 +2007,7 @@
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="11" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A10&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A10-ボード!$B$4),FV(前提!$B$7,A10-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A10&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A10-ボード!$B$4),FV(前提!$B$7,A10-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>283344.472934632</v>
       </c>
     </row>
@@ -1964,7 +2021,7 @@
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="11" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A11&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A11-ボード!$B$4),FV(前提!$B$7,A11-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A11&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A11-ボード!$B$4),FV(前提!$B$7,A11-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>316653.502803418</v>
       </c>
     </row>
@@ -1978,7 +2035,7 @@
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="11" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A12&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A12-ボード!$B$4),FV(前提!$B$7,A12-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A12&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A12-ボード!$B$4),FV(前提!$B$7,A12-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>350043.029494386</v>
       </c>
     </row>
@@ -1992,7 +2049,7 @@
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="11" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A13&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A13-ボード!$B$4),FV(前提!$B$7,A13-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A13&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A13-ボード!$B$4),FV(前提!$B$7,A13-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>383513.247541523</v>
       </c>
     </row>
@@ -2006,7 +2063,7 @@
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="11" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A14&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A14-ボード!$B$4),FV(前提!$B$7,A14-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A14&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A14-ボード!$B$4),FV(前提!$B$7,A14-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>417064.351948939</v>
       </c>
     </row>
@@ -2020,7 +2077,7 @@
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="11" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A15&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A15-ボード!$B$4),FV(前提!$B$7,A15-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A15&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A15-ボード!$B$4),FV(前提!$B$7,A15-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>450696.53819201</v>
       </c>
     </row>
@@ -2034,7 +2091,7 @@
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="11" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A16&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A16-ボード!$B$4),FV(前提!$B$7,A16-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A16&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A16-ボード!$B$4),FV(前提!$B$7,A16-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>484410.002218498</v>
       </c>
     </row>
@@ -2048,7 +2105,7 @@
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="11" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A17&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A17-ボード!$B$4),FV(前提!$B$7,A17-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A17&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A17-ボード!$B$4),FV(前提!$B$7,A17-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>518204.940449719</v>
       </c>
     </row>
@@ -2062,7 +2119,7 @@
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="11" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A18&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A18-ボード!$B$4),FV(前提!$B$7,A18-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A18&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A18-ボード!$B$4),FV(前提!$B$7,A18-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>552081.549781664</v>
       </c>
     </row>
@@ -2076,7 +2133,7 @@
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="11" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A19&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A19-ボード!$B$4),FV(前提!$B$7,A19-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A19&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A19-ボード!$B$4),FV(前提!$B$7,A19-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>586040.027586163</v>
       </c>
     </row>
@@ -2090,7 +2147,7 @@
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="11" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A20&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A20-ボード!$B$4),FV(前提!$B$7,A20-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A20&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A20-ボード!$B$4),FV(前提!$B$7,A20-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>620080.571712022</v>
       </c>
     </row>
@@ -2104,7 +2161,7 @@
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="11" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A21&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A21-ボード!$B$4),FV(前提!$B$7,A21-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A21&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A21-ボード!$B$4),FV(前提!$B$7,A21-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>654203.380486184</v>
       </c>
     </row>
@@ -2118,7 +2175,7 @@
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="11" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A22&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A22-ボード!$B$4),FV(前提!$B$7,A22-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A22&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A22-ボード!$B$4),FV(前提!$B$7,A22-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>688408.652714886</v>
       </c>
     </row>
@@ -2132,7 +2189,7 @@
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="11" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A23&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A23-ボード!$B$4),FV(前提!$B$7,A23-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A23&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A23-ボード!$B$4),FV(前提!$B$7,A23-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>722696.587684805</v>
       </c>
     </row>
@@ -2146,7 +2203,7 @@
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="11" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A24&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A24-ボード!$B$4),FV(前提!$B$7,A24-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A24&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A24-ボード!$B$4),FV(前提!$B$7,A24-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>757067.385164236</v>
       </c>
     </row>
@@ -2160,7 +2217,7 @@
       </c>
       <c r="C25" s="7"/>
       <c r="D25" s="11" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A25&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A25-ボード!$B$4),FV(前提!$B$7,A25-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A25&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A25-ボード!$B$4),FV(前提!$B$7,A25-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>791521.245404242</v>
       </c>
     </row>
@@ -2174,7 +2231,7 @@
       </c>
       <c r="C26" s="7"/>
       <c r="D26" s="11" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A26&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A26-ボード!$B$4),FV(前提!$B$7,A26-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A26&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A26-ボード!$B$4),FV(前提!$B$7,A26-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>826058.369139829</v>
       </c>
     </row>
@@ -2188,7 +2245,7 @@
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="11" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A27&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A27-ボード!$B$4),FV(前提!$B$7,A27-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A27&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A27-ボード!$B$4),FV(前提!$B$7,A27-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>860678.957591108</v>
       </c>
     </row>
@@ -2202,7 +2259,7 @@
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="11" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A28&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A28-ボード!$B$4),FV(前提!$B$7,A28-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A28&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A28-ボード!$B$4),FV(前提!$B$7,A28-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>895383.212464479</v>
       </c>
     </row>
@@ -2216,7 +2273,7 @@
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="11" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A29&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A29-ボード!$B$4),FV(前提!$B$7,A29-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A29&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A29-ボード!$B$4),FV(前提!$B$7,A29-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>930171.335953793</v>
       </c>
     </row>
@@ -2230,7 +2287,7 @@
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="11" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A30&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A30-ボード!$B$4),FV(前提!$B$7,A30-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A30&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A30-ボード!$B$4),FV(前提!$B$7,A30-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>965043.530741541</v>
       </c>
     </row>
@@ -2244,7 +2301,7 @@
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="11" t="n">
-        <f aca="false">IF(OR(ボード!$B$4="",A31&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A31-ボード!$B$4),FV(前提!$B$7,A31-ボード!$B$4,-ボード!$B$10,-ボード!$B$5)))</f>
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A31&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A31-ボード!$B$4),FV(前提!$B$7,A31-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>1000000.00000003</v>
       </c>
     </row>
@@ -2254,6 +2311,12 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" error="0以上の数字を入れてください" errorStyle="stop" errorTitle="入力の確認" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C2:C31" type="decimal">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2269,7 +2332,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="48"/>
@@ -2291,7 +2354,7 @@
         <v>25</v>
       </c>
       <c r="B4" s="13" t="n">
-        <f aca="false">IF(COUNT(記録!C2:C31)=0,"",COUNT(記録!C2:C31))</f>
+        <f aca="false">IF(COUNT(記録!C2:C31)=0,"",LOOKUP(2,1/(記録!C2:C31&lt;&gt;""),記録!A2:A31))</f>
         <v>4</v>
       </c>
     </row>
@@ -2318,7 +2381,7 @@
         <v>28</v>
       </c>
       <c r="B7" s="15" t="n">
-        <f aca="false">IFERROR((B5-前提!B2)/(前提!B3-前提!B2),"")</f>
+        <f aca="false">IF(OR(B4="",前提!B3=前提!B2),"",(B5-前提!B2)/(前提!B3-前提!B2))</f>
         <v>0.118</v>
       </c>
     </row>
@@ -2345,7 +2408,7 @@
         <v>31</v>
       </c>
       <c r="B10" s="14" t="n">
-        <f aca="false">IFERROR(IF(B9&lt;=0,"",IF(B5&gt;=前提!B3,0,IF(前提!B7=0,(前提!B3-B5)/B9,PMT(前提!B7,B9,B5,-前提!B3)))),"")</f>
+        <f aca="false">IF(B4="","",IF(B5&gt;=前提!B3,0,IF(B9&lt;=0,"",IF(前提!B7=0,(前提!B3-B5)/B9,PMT(前提!B7,B9,B5,-前提!B3)))))</f>
         <v>32624.2807258581</v>
       </c>
     </row>
@@ -2363,13 +2426,27 @@
         <v>33</v>
       </c>
       <c r="B12" s="14" t="n">
-        <f aca="false">IFERROR(IF(B9&lt;=0,B5,IF(前提!B7=0,B5+前提!B8*B9,FV(前提!B7,B9,-前提!B8,-B5))),"")</f>
+        <f aca="false">IF(B4="","",IF(B9&lt;=0,B5,IF(前提!B7=0,B5+前提!B8*B9,FV(前提!B7,B9,-前提!B8,-B5))))</f>
         <v>988088.717077351</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+    <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
         <v>34</v>
+      </c>
+      <c r="B13" s="17" t="str">
+        <f aca="false">IF(COUNTIF(記録!C2:C31,"&lt;0")&gt;0,"マイナスの値があります。確認してください",IF(B4="","実績を入力してください",IF(B9&lt;=0,"期限に達しました（前提の見直しが必要）",IF(COUNT(記録!C2:C31)&lt;B4,"入力していない月があります（現在地は最後に入力した月で計算）","OK"))))</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/docs/platform/p1-kit/boards/board-02-money.xlsx
+++ b/docs/platform/p1-kit/boards/board-02-money.xlsx
@@ -8,10 +8,11 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="使い方" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="前提" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="記録" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="ボード" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="スマホ" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="使い方" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="前提" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="記録" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="ボード" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,19 +24,41 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
-  <si>
-    <t xml:space="preserve">② 現在地ボード：家計・積立</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">毎月</t>
-    </r>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="77">
+  <si>
+    <t xml:space="preserve">② スマホで見る：家計・積立</t>
+  </si>
+  <si>
+    <t xml:space="preserve">■ 現在地</t>
+  </si>
+  <si>
+    <t xml:space="preserve">現在の積立残高</t>
+  </si>
+  <si>
+    <t xml:space="preserve">目標</t>
+  </si>
+  <si>
+    <t xml:space="preserve">進み具合</t>
+  </si>
+  <si>
+    <t xml:space="preserve">計画と比べて</t>
+  </si>
+  <si>
+    <t xml:space="preserve">目標に必要な毎月の積立額（更新後）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">今の積立額を続けた場合の期限時点（仮定）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">入力のチェック</t>
+  </si>
+  <si>
+    <t xml:space="preserve">単位：円。仮定の利回りによる計算で、予測・保証ではありません。元本割れのリスクがあります。税金は含みません。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">■ 毎月の数字を入れる：月末の積立残高（円）</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -51,21 +74,10 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">回、「記録」シートの「実績」に、月末の積立残高（評価額のおおよその額）を入れてください。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">入れると、現在地・目標までの進み具合と、期限までに目標に届くために必要な毎月の積立額が自動で計算され、残りの月の予定が作り直されます。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">利回りは仮定です（予測・保証ではありません）。</t>
-    </r>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -73,7 +85,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">0%</t>
+      <t xml:space="preserve">2</t>
     </r>
     <r>
       <rPr>
@@ -81,8 +93,10 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">やマイナスでも試してください。税金（課税口座は利益に原則</t>
-    </r>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -90,7 +104,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">20.315%</t>
+      <t xml:space="preserve">3</t>
     </r>
     <r>
       <rPr>
@@ -98,33 +112,10 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">）は含みません。銘柄や商品の選び方の助言は含みません。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">凡例</t>
-  </si>
-  <si>
-    <t xml:space="preserve">黄色のセル（青字）＝あなたが入力する欄</t>
-  </si>
-  <si>
-    <t xml:space="preserve">緑のセル＝自動で計算される「現在地」と「これからの予定」</t>
-  </si>
-  <si>
-    <t xml:space="preserve">その他の白いセル＝自動計算（触らない）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">入っている数字は架空の記入例です。上書きしてお使いください。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">このシートは、入力した数字から機械的に計算した目安です。結果を保証するものではありません。氏名・口座番号・</t>
-    </r>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -132,7 +123,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">ID</t>
+      <t xml:space="preserve">4</t>
     </r>
     <r>
       <rPr>
@@ -140,6 +131,619 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">13</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">17</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">18</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">19</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">23</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">24</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">25</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">26</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">27</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">28</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">29</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">か月目</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">② 現在地ボード：家計・積立</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">毎月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">回、「スマホ」シートの下にある「毎月の数字を入れる」欄に、月末の積立残高（評価額のおおよその額）を入れてください。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">入れると、現在地・目標までの進み具合と、期限までに目標に届くために必要な毎月の積立額が自動で計算され、残りの月の予定が作り直されます。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">利回りは仮定です（予測・保証ではありません）。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">やマイナスでも試してください。税金（課税口座は利益に原則</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20.315%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）は含みません。銘柄や商品の選び方の助言は含みません。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">凡例</t>
+  </si>
+  <si>
+    <t xml:space="preserve">黄色のセル（青字）＝あなたが入力する欄</t>
+  </si>
+  <si>
+    <t xml:space="preserve">緑のセル＝自動で計算される「現在地」と「これからの予定」</t>
+  </si>
+  <si>
+    <t xml:space="preserve">その他の白いセル＝自動計算（触らない）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">入っている数字は架空の記入例です。上書きしてお使いください。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">このシートは、入力した数字から機械的に計算した目安です。結果を保証するものではありません。氏名・口座番号・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ID</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">・パスワード・学校名などは書かないでください。</t>
     </r>
   </si>
@@ -174,13 +778,13 @@
     <t xml:space="preserve">当初の計画（円・仮定）</t>
   </si>
   <si>
-    <t xml:space="preserve">実績（円）※入力</t>
+    <t xml:space="preserve">実績（円）※スマホのシートから自動</t>
   </si>
   <si>
     <t xml:space="preserve">更新後の予定（円・仮定）</t>
   </si>
   <si>
-    <t xml:space="preserve">※ 入力するのは「実績」の列だけです。</t>
+    <t xml:space="preserve">※ 実績は「スマホ」シートで入力します（この列は自動）。</t>
   </si>
   <si>
     <t xml:space="preserve">現在地ボード：家計・積立（仮定条件にもとづく試算）</t>
@@ -214,9 +818,6 @@
   </si>
   <si>
     <t xml:space="preserve">当初の積立額を続けた場合の期限時点の残高（円・仮定）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">入力のチェック</t>
   </si>
   <si>
     <r>
@@ -273,12 +874,12 @@
   <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
-    <numFmt numFmtId="166" formatCode="0"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
-    <numFmt numFmtId="168" formatCode="0.000%"/>
-    <numFmt numFmtId="169" formatCode="0%"/>
+    <numFmt numFmtId="166" formatCode="0%"/>
+    <numFmt numFmtId="167" formatCode="0"/>
+    <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="169" formatCode="0.000%"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -303,7 +904,13 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="14"/>
+      <sz val="13"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
     </font>
@@ -313,33 +920,26 @@
       <family val="2"/>
     </font>
     <font>
+      <b val="true"/>
       <sz val="11"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
       <sz val="11"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -364,6 +964,18 @@
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -374,14 +986,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFE2F0D9"/>
+        <fgColor rgb="FFE2F0D9"/>
+        <bgColor rgb="FFDDE6F5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2F0D9"/>
-        <bgColor rgb="FFDDE6F5"/>
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFE2F0D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -440,76 +1052,100 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -611,7 +1247,7 @@
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:rPr>
-              <a:t>当初の計画・実績・更新後の予定（仮定）</a:t>
+              <a:t>計画・実績・予定（仮定）</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -634,11 +1270,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>記録!B1</c:f>
+              <c:f>"当初の計画"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>当初の計画（円・仮定）</c:v>
+                  <c:v>当初の計画</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -886,11 +1522,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>記録!C1</c:f>
+              <c:f>"実績"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>実績（円）※入力</c:v>
+                  <c:v>実績</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1034,7 +1670,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>記録!$C$2:$C$31</c:f>
+              <c:f>スマホ!$B$27:$B$56</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="30"/>
@@ -1060,11 +1696,11 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>記録!D1</c:f>
+              <c:f>"更新後の予定"</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>更新後の予定（円・仮定）</c:v>
+                  <c:v>更新後の予定</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1303,11 +1939,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="82735445"/>
-        <c:axId val="1061964"/>
+        <c:axId val="49162816"/>
+        <c:axId val="49709446"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="82735445"/>
+        <c:axId val="49162816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1339,7 +1975,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1061964"/>
+        <c:crossAx val="49709446"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1347,7 +1983,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1061964"/>
+        <c:axId val="49709446"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1423,7 +2059,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="82735445"/>
+        <c:crossAx val="49162816"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1435,7 +2071,897 @@
       </c:spPr>
     </c:plotArea>
     <c:legend>
-      <c:legendPos val="r"/>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="d9d9d9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr b="1" sz="1800" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>当初の計画・実績・更新後の予定（仮定）</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"当初の計画"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>当初の計画</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4a7ebb"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="4a7ebb"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>記録!$A$2:$A$31</c:f>
+              <c:strCache>
+                <c:ptCount val="30"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>記録!$B$2:$B$31</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="30"/>
+                <c:pt idx="0">
+                  <c:v>32179.84338037</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>64437.4547155767</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>96773.0219448413</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>129186.733461579</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>161678.778114479</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>194249.345208628</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>226898.624506586</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>259626.806229513</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>292434.081058269</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>325320.640134532</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>358286.675061893</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>391332.377906997</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>424457.941200641</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>457663.557938913</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>490949.421584303</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>524315.726066834</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>557762.6657852</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>591290.435607884</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>624899.230874306</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>658589.247395956</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>692360.681457534</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>726213.729818092</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>760148.589712189</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>794165.45885103</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>828264.535423623</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>862446.018097934</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>896710.106022042</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>931056.998825299</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>965486.896619496</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1000000.00000003</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"実績"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>実績</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="be4b48"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="be4b48"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>記録!$A$2:$A$31</c:f>
+              <c:strCache>
+                <c:ptCount val="30"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>スマホ!$B$27:$B$56</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="30"/>
+                <c:pt idx="0">
+                  <c:v>30500</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>61000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>90000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>118000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"更新後の予定"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>更新後の予定</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="98b855"/>
+            </a:solidFill>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="98b855"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>記録!$A$2:$A$31</c:f>
+              <c:strCache>
+                <c:ptCount val="30"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>記録!$D$2:$D$31</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="30"/>
+                <c:pt idx="4">
+                  <c:v>150909.447392526</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>183898.425949584</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>216967.127871486</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>250115.745823035</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>283344.472934632</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>316653.502803418</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>350043.029494386</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>383513.247541523</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>417064.351948939</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>450696.53819201</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>484410.002218498</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>518204.940449719</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>552081.549781664</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>586040.027586163</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>620080.571712022</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>654203.380486184</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>688408.652714886</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>722696.587684805</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>757067.385164236</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>791521.245404242</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>826058.369139829</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>860678.957591108</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>895383.212464479</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>930171.335953793</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>965043.530741541</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1000000.00000003</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="0"/>
+        <c:axId val="37083562"/>
+        <c:axId val="68112647"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="37083562"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="68112647"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="68112647"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="878787"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="1" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="1" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>円</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="#,##0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="37083562"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1479,6 +3005,41 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>593280</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>129600</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>122040</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="0" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="5143680"/>
+        <a:ext cx="3419640" cy="2519640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
@@ -1492,7 +3053,7 @@
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="0" name="Chart 1"/>
+        <xdr:cNvPr id="1" name="Chart 1"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1690,63 +3251,295 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:B56"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="110"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="38.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+    <row r="3" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="B3" s="4" t="n">
+        <f aca="false">ボード!B5</f>
+        <v>118000</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="5" t="n">
+        <f aca="false">ボード!B6</f>
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="n">
+        <f aca="false">ボード!B7</f>
+        <v>0.118</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="str">
+        <f aca="false">ボード!B8</f>
+        <v>計画より遅れ</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="B7" s="4" t="n">
+        <f aca="false">ボード!B10</f>
+        <v>32624.2807258581</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="B8" s="5" t="n">
+        <f aca="false">ボード!B12</f>
+        <v>988088.717077351</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+      <c r="B9" s="3" t="str">
+        <f aca="false">ボード!B13</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
         <v>9</v>
       </c>
+      <c r="B10" s="7"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" s="9" t="n">
+        <v>30500</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" s="9" t="n">
+        <v>61000</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" s="9" t="n">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="9" t="n">
+        <v>118000</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" s="9"/>
+    </row>
+    <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32" s="9"/>
+    </row>
+    <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" s="9"/>
+    </row>
+    <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B34" s="9"/>
+    </row>
+    <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B35" s="9"/>
+    </row>
+    <row r="36" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B36" s="9"/>
+    </row>
+    <row r="37" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37" s="9"/>
+    </row>
+    <row r="38" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B38" s="9"/>
+    </row>
+    <row r="39" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B39" s="9"/>
+    </row>
+    <row r="40" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B40" s="9"/>
+    </row>
+    <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B41" s="9"/>
+    </row>
+    <row r="42" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B42" s="9"/>
+    </row>
+    <row r="43" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B43" s="9"/>
+    </row>
+    <row r="44" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B44" s="9"/>
+    </row>
+    <row r="45" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B45" s="9"/>
+    </row>
+    <row r="46" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B46" s="9"/>
+    </row>
+    <row r="47" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B47" s="9"/>
+    </row>
+    <row r="48" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B48" s="9"/>
+    </row>
+    <row r="49" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B49" s="9"/>
+    </row>
+    <row r="50" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B50" s="9"/>
+    </row>
+    <row r="51" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B51" s="9"/>
+    </row>
+    <row r="52" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B52" s="9"/>
+    </row>
+    <row r="53" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" s="9"/>
+    </row>
+    <row r="54" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" s="9"/>
+    </row>
+    <row r="55" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" s="9"/>
+    </row>
+    <row r="56" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="9"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A10:B10"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" error="0以上の数字を入れてください" errorStyle="stop" errorTitle="入力の確認" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B27:B56" type="decimal">
+      <formula1>0</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1754,6 +3547,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1762,83 +3556,63 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="110"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="7" t="n">
-        <v>0</v>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="10" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="7" t="n">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="8" t="n">
-        <v>30</v>
+      <c r="A3" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="11" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="9" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="9" t="n">
-        <v>0.001</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="10" t="n">
-        <f aca="false">(B5-B6)/12</f>
-        <v>0.00241666666666667</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="11" t="n">
-        <f aca="false">IF(B7=0,(B3-B2)/B4,PMT(B7,B4,B2,-B3))</f>
-        <v>32179.8433803691</v>
+      <c r="A5" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="11" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation allowBlank="true" error="0以上の数字を入れてください" errorStyle="stop" errorTitle="入力の確認" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B2:B4" type="decimal">
-      <formula1>0</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1854,465 +3628,79 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="11" t="n">
-        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A2,FV(前提!$B$7,A2,-前提!$B$8,-前提!$B$2))</f>
-        <v>32179.84338037</v>
-      </c>
-      <c r="C2" s="7" t="n">
-        <v>30500</v>
-      </c>
-      <c r="D2" s="11" t="str">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A2&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A2-ボード!$B$4),FV(前提!$B$7,A2-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="11" t="n">
-        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A3,FV(前提!$B$7,A3,-前提!$B$8,-前提!$B$2))</f>
-        <v>64437.4547155767</v>
-      </c>
-      <c r="C3" s="7" t="n">
-        <v>61000</v>
-      </c>
-      <c r="D3" s="11" t="str">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A3&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A3-ボード!$B$4),FV(前提!$B$7,A3-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="11" t="n">
-        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A4,FV(前提!$B$7,A4,-前提!$B$8,-前提!$B$2))</f>
-        <v>96773.0219448413</v>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>90000</v>
-      </c>
-      <c r="D4" s="11" t="str">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A4&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A4-ボード!$B$4),FV(前提!$B$7,A4-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="11" t="n">
-        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A5,FV(前提!$B$7,A5,-前提!$B$8,-前提!$B$2))</f>
-        <v>129186.733461579</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>118000</v>
-      </c>
-      <c r="D5" s="11" t="str">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A5&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A5-ボード!$B$4),FV(前提!$B$7,A5-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="11" t="n">
-        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A6,FV(前提!$B$7,A6,-前提!$B$8,-前提!$B$2))</f>
-        <v>161678.778114479</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="11" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A6&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A6-ボード!$B$4),FV(前提!$B$7,A6-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
-        <v>150909.447392526</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="11" t="n">
-        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A7,FV(前提!$B$7,A7,-前提!$B$8,-前提!$B$2))</f>
-        <v>194249.345208628</v>
-      </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="11" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A7&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A7-ボード!$B$4),FV(前提!$B$7,A7-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
-        <v>183898.425949584</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="11" t="n">
-        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A8,FV(前提!$B$7,A8,-前提!$B$8,-前提!$B$2))</f>
-        <v>226898.624506586</v>
-      </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="11" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A8&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A8-ボード!$B$4),FV(前提!$B$7,A8-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
-        <v>216967.127871486</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="11" t="n">
-        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A9,FV(前提!$B$7,A9,-前提!$B$8,-前提!$B$2))</f>
-        <v>259626.806229513</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="11" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A9&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A9-ボード!$B$4),FV(前提!$B$7,A9-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
-        <v>250115.745823035</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="11" t="n">
-        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A10,FV(前提!$B$7,A10,-前提!$B$8,-前提!$B$2))</f>
-        <v>292434.081058269</v>
-      </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="11" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A10&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A10-ボード!$B$4),FV(前提!$B$7,A10-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
-        <v>283344.472934632</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="11" t="n">
-        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A11,FV(前提!$B$7,A11,-前提!$B$8,-前提!$B$2))</f>
-        <v>325320.640134532</v>
-      </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="11" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A11&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A11-ボード!$B$4),FV(前提!$B$7,A11-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
-        <v>316653.502803418</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="11" t="n">
-        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A12,FV(前提!$B$7,A12,-前提!$B$8,-前提!$B$2))</f>
-        <v>358286.675061893</v>
-      </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="11" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A12&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A12-ボード!$B$4),FV(前提!$B$7,A12-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
-        <v>350043.029494386</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="11" t="n">
-        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A13,FV(前提!$B$7,A13,-前提!$B$8,-前提!$B$2))</f>
-        <v>391332.377906997</v>
-      </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="11" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A13&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A13-ボード!$B$4),FV(前提!$B$7,A13-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
-        <v>383513.247541523</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="11" t="n">
-        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A14,FV(前提!$B$7,A14,-前提!$B$8,-前提!$B$2))</f>
-        <v>424457.941200641</v>
-      </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="11" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A14&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A14-ボード!$B$4),FV(前提!$B$7,A14-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
-        <v>417064.351948939</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="11" t="n">
-        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A15,FV(前提!$B$7,A15,-前提!$B$8,-前提!$B$2))</f>
-        <v>457663.557938913</v>
-      </c>
-      <c r="C15" s="7"/>
-      <c r="D15" s="11" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A15&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A15-ボード!$B$4),FV(前提!$B$7,A15-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
-        <v>450696.53819201</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="11" t="n">
-        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A16,FV(前提!$B$7,A16,-前提!$B$8,-前提!$B$2))</f>
-        <v>490949.421584303</v>
-      </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="11" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A16&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A16-ボード!$B$4),FV(前提!$B$7,A16-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
-        <v>484410.002218498</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="11" t="n">
-        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A17,FV(前提!$B$7,A17,-前提!$B$8,-前提!$B$2))</f>
-        <v>524315.726066834</v>
-      </c>
-      <c r="C17" s="7"/>
-      <c r="D17" s="11" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A17&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A17-ボード!$B$4),FV(前提!$B$7,A17-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
-        <v>518204.940449719</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="11" t="n">
-        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A18,FV(前提!$B$7,A18,-前提!$B$8,-前提!$B$2))</f>
-        <v>557762.6657852</v>
-      </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="11" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A18&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A18-ボード!$B$4),FV(前提!$B$7,A18-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
-        <v>552081.549781664</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="11" t="n">
-        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A19,FV(前提!$B$7,A19,-前提!$B$8,-前提!$B$2))</f>
-        <v>591290.435607884</v>
-      </c>
-      <c r="C19" s="7"/>
-      <c r="D19" s="11" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A19&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A19-ボード!$B$4),FV(前提!$B$7,A19-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
-        <v>586040.027586163</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="11" t="n">
-        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A20,FV(前提!$B$7,A20,-前提!$B$8,-前提!$B$2))</f>
-        <v>624899.230874306</v>
-      </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="11" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A20&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A20-ボード!$B$4),FV(前提!$B$7,A20-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
-        <v>620080.571712022</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="11" t="n">
-        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A21,FV(前提!$B$7,A21,-前提!$B$8,-前提!$B$2))</f>
-        <v>658589.247395956</v>
-      </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="11" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A21&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A21-ボード!$B$4),FV(前提!$B$7,A21-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
-        <v>654203.380486184</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="11" t="n">
-        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A22,FV(前提!$B$7,A22,-前提!$B$8,-前提!$B$2))</f>
-        <v>692360.681457534</v>
-      </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="11" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A22&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A22-ボード!$B$4),FV(前提!$B$7,A22-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
-        <v>688408.652714886</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="11" t="n">
-        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A23,FV(前提!$B$7,A23,-前提!$B$8,-前提!$B$2))</f>
-        <v>726213.729818092</v>
-      </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="11" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A23&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A23-ボード!$B$4),FV(前提!$B$7,A23-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
-        <v>722696.587684805</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="11" t="n">
-        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A24,FV(前提!$B$7,A24,-前提!$B$8,-前提!$B$2))</f>
-        <v>760148.589712189</v>
-      </c>
-      <c r="C24" s="7"/>
-      <c r="D24" s="11" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A24&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A24-ボード!$B$4),FV(前提!$B$7,A24-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
-        <v>757067.385164236</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="13" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="11" t="n">
-        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A25,FV(前提!$B$7,A25,-前提!$B$8,-前提!$B$2))</f>
-        <v>794165.45885103</v>
-      </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="11" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A25&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A25-ボード!$B$4),FV(前提!$B$7,A25-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
-        <v>791521.245404242</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="13" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="11" t="n">
-        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A26,FV(前提!$B$7,A26,-前提!$B$8,-前提!$B$2))</f>
-        <v>828264.535423623</v>
-      </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="11" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A26&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A26-ボード!$B$4),FV(前提!$B$7,A26-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
-        <v>826058.369139829</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="11" t="n">
-        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A27,FV(前提!$B$7,A27,-前提!$B$8,-前提!$B$2))</f>
-        <v>862446.018097934</v>
-      </c>
-      <c r="C27" s="7"/>
-      <c r="D27" s="11" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A27&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A27-ボード!$B$4),FV(前提!$B$7,A27-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
-        <v>860678.957591108</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="11" t="n">
-        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A28,FV(前提!$B$7,A28,-前提!$B$8,-前提!$B$2))</f>
-        <v>896710.106022042</v>
-      </c>
-      <c r="C28" s="7"/>
-      <c r="D28" s="11" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A28&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A28-ボード!$B$4),FV(前提!$B$7,A28-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
-        <v>895383.212464479</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="11" t="n">
-        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A29,FV(前提!$B$7,A29,-前提!$B$8,-前提!$B$2))</f>
-        <v>931056.998825299</v>
-      </c>
-      <c r="C29" s="7"/>
-      <c r="D29" s="11" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A29&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A29-ボード!$B$4),FV(前提!$B$7,A29-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
-        <v>930171.335953793</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="11" t="n">
-        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A30,FV(前提!$B$7,A30,-前提!$B$8,-前提!$B$2))</f>
-        <v>965486.896619496</v>
-      </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="11" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A30&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A30-ボード!$B$4),FV(前提!$B$7,A30-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
-        <v>965043.530741541</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13" t="n">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="9" t="n">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="11" t="n">
-        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A31,FV(前提!$B$7,A31,-前提!$B$8,-前提!$B$2))</f>
-        <v>1000000.00000003</v>
-      </c>
-      <c r="C31" s="7"/>
-      <c r="D31" s="11" t="n">
-        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A31&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A31-ボード!$B$4),FV(前提!$B$7,A31-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
-        <v>1000000.00000003</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
-        <v>22</v>
+    </row>
+    <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="15" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" s="16" t="n">
+        <f aca="false">(B5-B6)/12</f>
+        <v>0.00241666666666667</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="17" t="n">
+        <f aca="false">IF(B7=0,(B3-B2)/B4,PMT(B7,B4,B2,-B3))</f>
+        <v>32179.8433803691</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" error="0以上の数字を入れてください" errorStyle="stop" errorTitle="入力の確認" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C2:C31" type="decimal">
+    <dataValidation allowBlank="true" error="0以上の数字を入れてください" errorStyle="stop" errorTitle="入力の確認" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B2:B4" type="decimal">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2332,6 +3720,560 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:D33"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="17" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A2,FV(前提!$B$7,A2,-前提!$B$8,-前提!$B$2))</f>
+        <v>32179.84338037</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <f aca="false">IF(スマホ!B27="","",スマホ!B27)</f>
+        <v>30500</v>
+      </c>
+      <c r="D2" s="17" t="str">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A2&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A2-ボード!$B$4),FV(前提!$B$7,A2-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="17" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A3,FV(前提!$B$7,A3,-前提!$B$8,-前提!$B$2))</f>
+        <v>64437.4547155767</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <f aca="false">IF(スマホ!B28="","",スマホ!B28)</f>
+        <v>61000</v>
+      </c>
+      <c r="D3" s="17" t="str">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A3&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A3-ボード!$B$4),FV(前提!$B$7,A3-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="17" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A4,FV(前提!$B$7,A4,-前提!$B$8,-前提!$B$2))</f>
+        <v>96773.0219448413</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <f aca="false">IF(スマホ!B29="","",スマホ!B29)</f>
+        <v>90000</v>
+      </c>
+      <c r="D4" s="17" t="str">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A4&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A4-ボード!$B$4),FV(前提!$B$7,A4-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="17" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A5,FV(前提!$B$7,A5,-前提!$B$8,-前提!$B$2))</f>
+        <v>129186.733461579</v>
+      </c>
+      <c r="C5" s="17" t="n">
+        <f aca="false">IF(スマホ!B30="","",スマホ!B30)</f>
+        <v>118000</v>
+      </c>
+      <c r="D5" s="17" t="str">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A5&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A5-ボード!$B$4),FV(前提!$B$7,A5-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="17" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A6,FV(前提!$B$7,A6,-前提!$B$8,-前提!$B$2))</f>
+        <v>161678.778114479</v>
+      </c>
+      <c r="C6" s="17" t="str">
+        <f aca="false">IF(スマホ!B31="","",スマホ!B31)</f>
+        <v/>
+      </c>
+      <c r="D6" s="17" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A6&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A6-ボード!$B$4),FV(前提!$B$7,A6-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
+        <v>150909.447392526</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="17" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A7,FV(前提!$B$7,A7,-前提!$B$8,-前提!$B$2))</f>
+        <v>194249.345208628</v>
+      </c>
+      <c r="C7" s="17" t="str">
+        <f aca="false">IF(スマホ!B32="","",スマホ!B32)</f>
+        <v/>
+      </c>
+      <c r="D7" s="17" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A7&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A7-ボード!$B$4),FV(前提!$B$7,A7-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
+        <v>183898.425949584</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="17" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A8,FV(前提!$B$7,A8,-前提!$B$8,-前提!$B$2))</f>
+        <v>226898.624506586</v>
+      </c>
+      <c r="C8" s="17" t="str">
+        <f aca="false">IF(スマホ!B33="","",スマホ!B33)</f>
+        <v/>
+      </c>
+      <c r="D8" s="17" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A8&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A8-ボード!$B$4),FV(前提!$B$7,A8-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
+        <v>216967.127871486</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="17" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A9,FV(前提!$B$7,A9,-前提!$B$8,-前提!$B$2))</f>
+        <v>259626.806229513</v>
+      </c>
+      <c r="C9" s="17" t="str">
+        <f aca="false">IF(スマホ!B34="","",スマホ!B34)</f>
+        <v/>
+      </c>
+      <c r="D9" s="17" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A9&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A9-ボード!$B$4),FV(前提!$B$7,A9-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
+        <v>250115.745823035</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="17" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A10,FV(前提!$B$7,A10,-前提!$B$8,-前提!$B$2))</f>
+        <v>292434.081058269</v>
+      </c>
+      <c r="C10" s="17" t="str">
+        <f aca="false">IF(スマホ!B35="","",スマホ!B35)</f>
+        <v/>
+      </c>
+      <c r="D10" s="17" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A10&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A10-ボード!$B$4),FV(前提!$B$7,A10-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
+        <v>283344.472934632</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="17" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A11,FV(前提!$B$7,A11,-前提!$B$8,-前提!$B$2))</f>
+        <v>325320.640134532</v>
+      </c>
+      <c r="C11" s="17" t="str">
+        <f aca="false">IF(スマホ!B36="","",スマホ!B36)</f>
+        <v/>
+      </c>
+      <c r="D11" s="17" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A11&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A11-ボード!$B$4),FV(前提!$B$7,A11-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
+        <v>316653.502803418</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="17" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A12,FV(前提!$B$7,A12,-前提!$B$8,-前提!$B$2))</f>
+        <v>358286.675061893</v>
+      </c>
+      <c r="C12" s="17" t="str">
+        <f aca="false">IF(スマホ!B37="","",スマホ!B37)</f>
+        <v/>
+      </c>
+      <c r="D12" s="17" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A12&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A12-ボード!$B$4),FV(前提!$B$7,A12-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
+        <v>350043.029494386</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="17" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A13,FV(前提!$B$7,A13,-前提!$B$8,-前提!$B$2))</f>
+        <v>391332.377906997</v>
+      </c>
+      <c r="C13" s="17" t="str">
+        <f aca="false">IF(スマホ!B38="","",スマホ!B38)</f>
+        <v/>
+      </c>
+      <c r="D13" s="17" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A13&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A13-ボード!$B$4),FV(前提!$B$7,A13-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
+        <v>383513.247541523</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="19" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="17" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A14,FV(前提!$B$7,A14,-前提!$B$8,-前提!$B$2))</f>
+        <v>424457.941200641</v>
+      </c>
+      <c r="C14" s="17" t="str">
+        <f aca="false">IF(スマホ!B39="","",スマホ!B39)</f>
+        <v/>
+      </c>
+      <c r="D14" s="17" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A14&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A14-ボード!$B$4),FV(前提!$B$7,A14-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
+        <v>417064.351948939</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="17" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A15,FV(前提!$B$7,A15,-前提!$B$8,-前提!$B$2))</f>
+        <v>457663.557938913</v>
+      </c>
+      <c r="C15" s="17" t="str">
+        <f aca="false">IF(スマホ!B40="","",スマホ!B40)</f>
+        <v/>
+      </c>
+      <c r="D15" s="17" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A15&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A15-ボード!$B$4),FV(前提!$B$7,A15-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
+        <v>450696.53819201</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="17" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A16,FV(前提!$B$7,A16,-前提!$B$8,-前提!$B$2))</f>
+        <v>490949.421584303</v>
+      </c>
+      <c r="C16" s="17" t="str">
+        <f aca="false">IF(スマホ!B41="","",スマホ!B41)</f>
+        <v/>
+      </c>
+      <c r="D16" s="17" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A16&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A16-ボード!$B$4),FV(前提!$B$7,A16-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
+        <v>484410.002218498</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="17" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A17,FV(前提!$B$7,A17,-前提!$B$8,-前提!$B$2))</f>
+        <v>524315.726066834</v>
+      </c>
+      <c r="C17" s="17" t="str">
+        <f aca="false">IF(スマホ!B42="","",スマホ!B42)</f>
+        <v/>
+      </c>
+      <c r="D17" s="17" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A17&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A17-ボード!$B$4),FV(前提!$B$7,A17-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
+        <v>518204.940449719</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="17" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A18,FV(前提!$B$7,A18,-前提!$B$8,-前提!$B$2))</f>
+        <v>557762.6657852</v>
+      </c>
+      <c r="C18" s="17" t="str">
+        <f aca="false">IF(スマホ!B43="","",スマホ!B43)</f>
+        <v/>
+      </c>
+      <c r="D18" s="17" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A18&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A18-ボード!$B$4),FV(前提!$B$7,A18-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
+        <v>552081.549781664</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="17" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A19,FV(前提!$B$7,A19,-前提!$B$8,-前提!$B$2))</f>
+        <v>591290.435607884</v>
+      </c>
+      <c r="C19" s="17" t="str">
+        <f aca="false">IF(スマホ!B44="","",スマホ!B44)</f>
+        <v/>
+      </c>
+      <c r="D19" s="17" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A19&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A19-ボード!$B$4),FV(前提!$B$7,A19-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
+        <v>586040.027586163</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="19" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="17" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A20,FV(前提!$B$7,A20,-前提!$B$8,-前提!$B$2))</f>
+        <v>624899.230874306</v>
+      </c>
+      <c r="C20" s="17" t="str">
+        <f aca="false">IF(スマホ!B45="","",スマホ!B45)</f>
+        <v/>
+      </c>
+      <c r="D20" s="17" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A20&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A20-ボード!$B$4),FV(前提!$B$7,A20-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
+        <v>620080.571712022</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="17" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A21,FV(前提!$B$7,A21,-前提!$B$8,-前提!$B$2))</f>
+        <v>658589.247395956</v>
+      </c>
+      <c r="C21" s="17" t="str">
+        <f aca="false">IF(スマホ!B46="","",スマホ!B46)</f>
+        <v/>
+      </c>
+      <c r="D21" s="17" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A21&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A21-ボード!$B$4),FV(前提!$B$7,A21-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
+        <v>654203.380486184</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="19" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="17" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A22,FV(前提!$B$7,A22,-前提!$B$8,-前提!$B$2))</f>
+        <v>692360.681457534</v>
+      </c>
+      <c r="C22" s="17" t="str">
+        <f aca="false">IF(スマホ!B47="","",スマホ!B47)</f>
+        <v/>
+      </c>
+      <c r="D22" s="17" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A22&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A22-ボード!$B$4),FV(前提!$B$7,A22-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
+        <v>688408.652714886</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="17" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A23,FV(前提!$B$7,A23,-前提!$B$8,-前提!$B$2))</f>
+        <v>726213.729818092</v>
+      </c>
+      <c r="C23" s="17" t="str">
+        <f aca="false">IF(スマホ!B48="","",スマホ!B48)</f>
+        <v/>
+      </c>
+      <c r="D23" s="17" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A23&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A23-ボード!$B$4),FV(前提!$B$7,A23-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
+        <v>722696.587684805</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="19" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="17" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A24,FV(前提!$B$7,A24,-前提!$B$8,-前提!$B$2))</f>
+        <v>760148.589712189</v>
+      </c>
+      <c r="C24" s="17" t="str">
+        <f aca="false">IF(スマホ!B49="","",スマホ!B49)</f>
+        <v/>
+      </c>
+      <c r="D24" s="17" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A24&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A24-ボード!$B$4),FV(前提!$B$7,A24-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
+        <v>757067.385164236</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="17" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A25,FV(前提!$B$7,A25,-前提!$B$8,-前提!$B$2))</f>
+        <v>794165.45885103</v>
+      </c>
+      <c r="C25" s="17" t="str">
+        <f aca="false">IF(スマホ!B50="","",スマホ!B50)</f>
+        <v/>
+      </c>
+      <c r="D25" s="17" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A25&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A25-ボード!$B$4),FV(前提!$B$7,A25-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
+        <v>791521.245404242</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="17" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A26,FV(前提!$B$7,A26,-前提!$B$8,-前提!$B$2))</f>
+        <v>828264.535423623</v>
+      </c>
+      <c r="C26" s="17" t="str">
+        <f aca="false">IF(スマホ!B51="","",スマホ!B51)</f>
+        <v/>
+      </c>
+      <c r="D26" s="17" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A26&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A26-ボード!$B$4),FV(前提!$B$7,A26-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
+        <v>826058.369139829</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="19" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="17" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A27,FV(前提!$B$7,A27,-前提!$B$8,-前提!$B$2))</f>
+        <v>862446.018097934</v>
+      </c>
+      <c r="C27" s="17" t="str">
+        <f aca="false">IF(スマホ!B52="","",スマホ!B52)</f>
+        <v/>
+      </c>
+      <c r="D27" s="17" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A27&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A27-ボード!$B$4),FV(前提!$B$7,A27-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
+        <v>860678.957591108</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="19" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="17" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A28,FV(前提!$B$7,A28,-前提!$B$8,-前提!$B$2))</f>
+        <v>896710.106022042</v>
+      </c>
+      <c r="C28" s="17" t="str">
+        <f aca="false">IF(スマホ!B53="","",スマホ!B53)</f>
+        <v/>
+      </c>
+      <c r="D28" s="17" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A28&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A28-ボード!$B$4),FV(前提!$B$7,A28-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
+        <v>895383.212464479</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="19" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="17" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A29,FV(前提!$B$7,A29,-前提!$B$8,-前提!$B$2))</f>
+        <v>931056.998825299</v>
+      </c>
+      <c r="C29" s="17" t="str">
+        <f aca="false">IF(スマホ!B54="","",スマホ!B54)</f>
+        <v/>
+      </c>
+      <c r="D29" s="17" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A29&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A29-ボード!$B$4),FV(前提!$B$7,A29-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
+        <v>930171.335953793</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="19" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="17" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A30,FV(前提!$B$7,A30,-前提!$B$8,-前提!$B$2))</f>
+        <v>965486.896619496</v>
+      </c>
+      <c r="C30" s="17" t="str">
+        <f aca="false">IF(スマホ!B55="","",スマホ!B55)</f>
+        <v/>
+      </c>
+      <c r="D30" s="17" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A30&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A30-ボード!$B$4),FV(前提!$B$7,A30-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
+        <v>965043.530741541</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="17" t="n">
+        <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A31,FV(前提!$B$7,A31,-前提!$B$8,-前提!$B$2))</f>
+        <v>1000000.00000003</v>
+      </c>
+      <c r="C31" s="17" t="str">
+        <f aca="false">IF(スマホ!B56="","",スマホ!B56)</f>
+        <v/>
+      </c>
+      <c r="D31" s="17" t="n">
+        <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A31&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A31-ボード!$B$4),FV(前提!$B$7,A31-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
+        <v>1000000.00000003</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:B16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -2340,113 +4282,113 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>23</v>
+      <c r="A1" s="10" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>24</v>
+      <c r="A3" s="2" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="13" t="n">
+      <c r="A4" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="19" t="n">
         <f aca="false">IF(COUNT(記録!C2:C31)=0,"",LOOKUP(2,1/(記録!C2:C31&lt;&gt;""),記録!A2:A31))</f>
         <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="14" t="n">
+      <c r="A5" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="20" t="n">
         <f aca="false">IF(B4="","",LOOKUP(2,1/(記録!C2:C31&lt;&gt;""),記録!C2:C31))</f>
         <v>118000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="11" t="n">
+      <c r="A6" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6" s="17" t="n">
         <f aca="false">前提!B3</f>
         <v>1000000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="15" t="n">
+      <c r="A7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="21" t="n">
         <f aca="false">IF(OR(B4="",前提!B3=前提!B2),"",(B5-前提!B2)/(前提!B3-前提!B2))</f>
         <v>0.118</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="16" t="str">
+      <c r="A8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="22" t="str">
         <f aca="false">IF(B4="","",IF(B5&gt;=INDEX(記録!B2:B31,B4),"計画どおり、または先行","計画より遅れ"))</f>
         <v>計画より遅れ</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="13" t="n">
+      <c r="A9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9" s="19" t="n">
         <f aca="false">IF(B4="","",前提!B4-B4)</f>
         <v>26</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="14" t="n">
+      <c r="A10" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="20" t="n">
         <f aca="false">IF(B4="","",IF(B5&gt;=前提!B3,0,IF(B9&lt;=0,"",IF(前提!B7=0,(前提!B3-B5)/B9,PMT(前提!B7,B9,B5,-前提!B3)))))</f>
         <v>32624.2807258581</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="11" t="n">
+      <c r="A11" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="17" t="n">
         <f aca="false">前提!B8</f>
         <v>32179.8433803691</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="14" t="n">
+      <c r="A12" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="20" t="n">
         <f aca="false">IF(B4="","",IF(B9&lt;=0,B5,IF(前提!B7=0,B5+前提!B8*B9,FV(前提!B7,B9,-前提!B8,-B5))))</f>
         <v>988088.717077351</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="17" t="str">
+      <c r="A13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="23" t="str">
         <f aca="false">IF(COUNTIF(記録!C2:C31,"&lt;0")&gt;0,"マイナスの値があります。確認してください",IF(B4="","実績を入力してください",IF(B9&lt;=0,"期限に達しました（前提の見直しが必要）",IF(COUNT(記録!C2:C31)&lt;B4,"入力していない月があります（現在地は最後に入力した月で計算）","OK"))))</f>
         <v>OK</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
-        <v>35</v>
+      <c r="A15" s="11" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
-        <v>36</v>
+      <c r="A16" s="11" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/docs/platform/p1-kit/boards/board-02-money.xlsx
+++ b/docs/platform/p1-kit/boards/board-02-money.xlsx
@@ -1939,11 +1939,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="49162816"/>
-        <c:axId val="49709446"/>
+        <c:axId val="23269538"/>
+        <c:axId val="51532058"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="49162816"/>
+        <c:axId val="23269538"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1975,7 +1975,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49709446"/>
+        <c:crossAx val="51532058"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1983,7 +1983,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="49709446"/>
+        <c:axId val="51532058"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2059,7 +2059,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49162816"/>
+        <c:crossAx val="23269538"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2829,11 +2829,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="37083562"/>
-        <c:axId val="68112647"/>
+        <c:axId val="70801563"/>
+        <c:axId val="57374544"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="37083562"/>
+        <c:axId val="70801563"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2865,7 +2865,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="68112647"/>
+        <c:crossAx val="57374544"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2873,7 +2873,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="68112647"/>
+        <c:axId val="57374544"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2949,7 +2949,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37083562"/>
+        <c:crossAx val="70801563"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4296,7 +4296,7 @@
         <v>66</v>
       </c>
       <c r="B4" s="19" t="n">
-        <f aca="false">IF(COUNT(記録!C2:C31)=0,"",LOOKUP(2,1/(記録!C2:C31&lt;&gt;""),記録!A2:A31))</f>
+        <f aca="false">IF(COUNT(記録!C2:C31)=0,"",INDEX(記録!A2:A31,MATCH(9.99E+307,記録!C2:C31)))</f>
         <v>4</v>
       </c>
     </row>
@@ -4305,7 +4305,7 @@
         <v>67</v>
       </c>
       <c r="B5" s="20" t="n">
-        <f aca="false">IF(B4="","",LOOKUP(2,1/(記録!C2:C31&lt;&gt;""),記録!C2:C31))</f>
+        <f aca="false">IF(B4="","",INDEX(記録!C2:C31,MATCH(9.99E+307,記録!C2:C31)))</f>
         <v>118000</v>
       </c>
     </row>

--- a/docs/platform/p1-kit/boards/board-02-money.xlsx
+++ b/docs/platform/p1-kit/boards/board-02-money.xlsx
@@ -1052,7 +1052,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1083,6 +1083,10 @@
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1939,11 +1943,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="23269538"/>
-        <c:axId val="51532058"/>
+        <c:axId val="92271248"/>
+        <c:axId val="30292359"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="23269538"/>
+        <c:axId val="92271248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1975,7 +1979,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="51532058"/>
+        <c:crossAx val="30292359"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1983,7 +1987,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="51532058"/>
+        <c:axId val="30292359"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2059,7 +2063,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="23269538"/>
+        <c:crossAx val="92271248"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2829,11 +2833,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="70801563"/>
-        <c:axId val="57374544"/>
+        <c:axId val="13163781"/>
+        <c:axId val="36922336"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="70801563"/>
+        <c:axId val="13163781"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2865,7 +2869,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="57374544"/>
+        <c:crossAx val="36922336"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2873,7 +2877,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="57374544"/>
+        <c:axId val="36922336"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2949,7 +2953,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70801563"/>
+        <c:crossAx val="13163781"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3338,201 +3342,203 @@
       <c r="B10" s="7"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="8" t="s">
         <v>10</v>
       </c>
+      <c r="B26" s="8"/>
     </row>
     <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B27" s="9" t="n">
+      <c r="B27" s="10" t="n">
         <v>30500</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="9" t="n">
+      <c r="B28" s="10" t="n">
         <v>61000</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B29" s="9" t="n">
+      <c r="B29" s="10" t="n">
         <v>90000</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B30" s="9" t="n">
+      <c r="B30" s="10" t="n">
         <v>118000</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="9"/>
+      <c r="B31" s="10"/>
     </row>
     <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="B32" s="9"/>
+      <c r="B32" s="10"/>
     </row>
     <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B33" s="9"/>
+      <c r="B33" s="10"/>
     </row>
     <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B34" s="9"/>
+      <c r="B34" s="10"/>
     </row>
     <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B35" s="9"/>
+      <c r="B35" s="10"/>
     </row>
     <row r="36" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B36" s="9"/>
+      <c r="B36" s="10"/>
     </row>
     <row r="37" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B37" s="9"/>
+      <c r="B37" s="10"/>
     </row>
     <row r="38" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B38" s="9"/>
+      <c r="B38" s="10"/>
     </row>
     <row r="39" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B39" s="9"/>
+      <c r="B39" s="10"/>
     </row>
     <row r="40" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B40" s="9"/>
+      <c r="B40" s="10"/>
     </row>
     <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B41" s="9"/>
+      <c r="B41" s="10"/>
     </row>
     <row r="42" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B42" s="9"/>
+      <c r="B42" s="10"/>
     </row>
     <row r="43" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B43" s="9"/>
+      <c r="B43" s="10"/>
     </row>
     <row r="44" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B44" s="9"/>
+      <c r="B44" s="10"/>
     </row>
     <row r="45" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B45" s="9"/>
+      <c r="B45" s="10"/>
     </row>
     <row r="46" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B46" s="9"/>
+      <c r="B46" s="10"/>
     </row>
     <row r="47" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B47" s="9"/>
+      <c r="B47" s="10"/>
     </row>
     <row r="48" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="8" t="s">
+      <c r="A48" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B48" s="9"/>
+      <c r="B48" s="10"/>
     </row>
     <row r="49" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B49" s="9"/>
+      <c r="B49" s="10"/>
     </row>
     <row r="50" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="8" t="s">
+      <c r="A50" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="B50" s="9"/>
+      <c r="B50" s="10"/>
     </row>
     <row r="51" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B51" s="9"/>
+      <c r="B51" s="10"/>
     </row>
     <row r="52" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="8" t="s">
+      <c r="A52" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B52" s="9"/>
+      <c r="B52" s="10"/>
     </row>
     <row r="53" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="8" t="s">
+      <c r="A53" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B53" s="9"/>
+      <c r="B53" s="10"/>
     </row>
     <row r="54" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="8" t="s">
+      <c r="A54" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B54" s="9"/>
+      <c r="B54" s="10"/>
     </row>
     <row r="55" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="8" t="s">
+      <c r="A55" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B55" s="9"/>
+      <c r="B55" s="10"/>
     </row>
     <row r="56" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="8" t="s">
+      <c r="A56" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B56" s="9"/>
+      <c r="B56" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A26:B26"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation allowBlank="true" error="0以上の数字を入れてください" errorStyle="stop" errorTitle="入力の確認" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="B27:B56" type="decimal">
@@ -3563,22 +3569,22 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="12" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="12" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="12" t="s">
         <v>44</v>
       </c>
     </row>
@@ -3588,27 +3594,27 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="13" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="14" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="12" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="12" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="12" t="s">
         <v>50</v>
       </c>
     </row>
@@ -3644,7 +3650,7 @@
       <c r="A2" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="9" t="n">
+      <c r="B2" s="10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3652,7 +3658,7 @@
       <c r="A3" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="9" t="n">
+      <c r="B3" s="10" t="n">
         <v>1000000</v>
       </c>
     </row>
@@ -3660,7 +3666,7 @@
       <c r="A4" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="14" t="n">
+      <c r="B4" s="15" t="n">
         <v>30</v>
       </c>
     </row>
@@ -3668,7 +3674,7 @@
       <c r="A5" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="15" t="n">
+      <c r="B5" s="16" t="n">
         <v>0.03</v>
       </c>
     </row>
@@ -3676,7 +3682,7 @@
       <c r="A6" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B6" s="15" t="n">
+      <c r="B6" s="16" t="n">
         <v>0.001</v>
       </c>
     </row>
@@ -3684,7 +3690,7 @@
       <c r="A7" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <f aca="false">(B5-B6)/12</f>
         <v>0.00241666666666667</v>
       </c>
@@ -3693,7 +3699,7 @@
       <c r="A8" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B8" s="18" t="n">
         <f aca="false">IF(B7=0,(B3-B2)/B4,PMT(B7,B4,B2,-B3))</f>
         <v>32179.8433803691</v>
       </c>
@@ -3730,531 +3736,531 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="19" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="19" t="n">
+      <c r="A2" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="17" t="n">
+      <c r="B2" s="18" t="n">
         <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A2,FV(前提!$B$7,A2,-前提!$B$8,-前提!$B$2))</f>
         <v>32179.84338037</v>
       </c>
-      <c r="C2" s="17" t="n">
+      <c r="C2" s="18" t="n">
         <f aca="false">IF(スマホ!B27="","",スマホ!B27)</f>
         <v>30500</v>
       </c>
-      <c r="D2" s="17" t="str">
+      <c r="D2" s="18" t="str">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A2&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A2-ボード!$B$4),FV(前提!$B$7,A2-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v/>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="n">
+      <c r="A3" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="17" t="n">
+      <c r="B3" s="18" t="n">
         <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A3,FV(前提!$B$7,A3,-前提!$B$8,-前提!$B$2))</f>
         <v>64437.4547155767</v>
       </c>
-      <c r="C3" s="17" t="n">
+      <c r="C3" s="18" t="n">
         <f aca="false">IF(スマホ!B28="","",スマホ!B28)</f>
         <v>61000</v>
       </c>
-      <c r="D3" s="17" t="str">
+      <c r="D3" s="18" t="str">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A3&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A3-ボード!$B$4),FV(前提!$B$7,A3-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v/>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="n">
+      <c r="A4" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="17" t="n">
+      <c r="B4" s="18" t="n">
         <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A4,FV(前提!$B$7,A4,-前提!$B$8,-前提!$B$2))</f>
         <v>96773.0219448413</v>
       </c>
-      <c r="C4" s="17" t="n">
+      <c r="C4" s="18" t="n">
         <f aca="false">IF(スマホ!B29="","",スマホ!B29)</f>
         <v>90000</v>
       </c>
-      <c r="D4" s="17" t="str">
+      <c r="D4" s="18" t="str">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A4&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A4-ボード!$B$4),FV(前提!$B$7,A4-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v/>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="n">
+      <c r="A5" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="17" t="n">
+      <c r="B5" s="18" t="n">
         <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A5,FV(前提!$B$7,A5,-前提!$B$8,-前提!$B$2))</f>
         <v>129186.733461579</v>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="C5" s="18" t="n">
         <f aca="false">IF(スマホ!B30="","",スマホ!B30)</f>
         <v>118000</v>
       </c>
-      <c r="D5" s="17" t="str">
+      <c r="D5" s="18" t="str">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A5&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A5-ボード!$B$4),FV(前提!$B$7,A5-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v/>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="n">
+      <c r="A6" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="18" t="n">
         <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A6,FV(前提!$B$7,A6,-前提!$B$8,-前提!$B$2))</f>
         <v>161678.778114479</v>
       </c>
-      <c r="C6" s="17" t="str">
+      <c r="C6" s="18" t="str">
         <f aca="false">IF(スマホ!B31="","",スマホ!B31)</f>
         <v/>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="18" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A6&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A6-ボード!$B$4),FV(前提!$B$7,A6-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>150909.447392526</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="17" t="n">
+      <c r="B7" s="18" t="n">
         <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A7,FV(前提!$B$7,A7,-前提!$B$8,-前提!$B$2))</f>
         <v>194249.345208628</v>
       </c>
-      <c r="C7" s="17" t="str">
+      <c r="C7" s="18" t="str">
         <f aca="false">IF(スマホ!B32="","",スマホ!B32)</f>
         <v/>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="18" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A7&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A7-ボード!$B$4),FV(前提!$B$7,A7-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>183898.425949584</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="n">
+      <c r="A8" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B8" s="18" t="n">
         <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A8,FV(前提!$B$7,A8,-前提!$B$8,-前提!$B$2))</f>
         <v>226898.624506586</v>
       </c>
-      <c r="C8" s="17" t="str">
+      <c r="C8" s="18" t="str">
         <f aca="false">IF(スマホ!B33="","",スマホ!B33)</f>
         <v/>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="18" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A8&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A8-ボード!$B$4),FV(前提!$B$7,A8-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>216967.127871486</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="19" t="n">
+      <c r="A9" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="17" t="n">
+      <c r="B9" s="18" t="n">
         <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A9,FV(前提!$B$7,A9,-前提!$B$8,-前提!$B$2))</f>
         <v>259626.806229513</v>
       </c>
-      <c r="C9" s="17" t="str">
+      <c r="C9" s="18" t="str">
         <f aca="false">IF(スマホ!B34="","",スマホ!B34)</f>
         <v/>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="18" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A9&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A9-ボード!$B$4),FV(前提!$B$7,A9-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>250115.745823035</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="19" t="n">
+      <c r="A10" s="20" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="17" t="n">
+      <c r="B10" s="18" t="n">
         <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A10,FV(前提!$B$7,A10,-前提!$B$8,-前提!$B$2))</f>
         <v>292434.081058269</v>
       </c>
-      <c r="C10" s="17" t="str">
+      <c r="C10" s="18" t="str">
         <f aca="false">IF(スマホ!B35="","",スマホ!B35)</f>
         <v/>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="18" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A10&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A10-ボード!$B$4),FV(前提!$B$7,A10-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>283344.472934632</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="19" t="n">
+      <c r="A11" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="17" t="n">
+      <c r="B11" s="18" t="n">
         <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A11,FV(前提!$B$7,A11,-前提!$B$8,-前提!$B$2))</f>
         <v>325320.640134532</v>
       </c>
-      <c r="C11" s="17" t="str">
+      <c r="C11" s="18" t="str">
         <f aca="false">IF(スマホ!B36="","",スマホ!B36)</f>
         <v/>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="18" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A11&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A11-ボード!$B$4),FV(前提!$B$7,A11-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>316653.502803418</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="19" t="n">
+      <c r="A12" s="20" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="17" t="n">
+      <c r="B12" s="18" t="n">
         <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A12,FV(前提!$B$7,A12,-前提!$B$8,-前提!$B$2))</f>
         <v>358286.675061893</v>
       </c>
-      <c r="C12" s="17" t="str">
+      <c r="C12" s="18" t="str">
         <f aca="false">IF(スマホ!B37="","",スマホ!B37)</f>
         <v/>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="18" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A12&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A12-ボード!$B$4),FV(前提!$B$7,A12-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>350043.029494386</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="n">
+      <c r="A13" s="20" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="17" t="n">
+      <c r="B13" s="18" t="n">
         <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A13,FV(前提!$B$7,A13,-前提!$B$8,-前提!$B$2))</f>
         <v>391332.377906997</v>
       </c>
-      <c r="C13" s="17" t="str">
+      <c r="C13" s="18" t="str">
         <f aca="false">IF(スマホ!B38="","",スマホ!B38)</f>
         <v/>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="18" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A13&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A13-ボード!$B$4),FV(前提!$B$7,A13-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>383513.247541523</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19" t="n">
+      <c r="A14" s="20" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="17" t="n">
+      <c r="B14" s="18" t="n">
         <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A14,FV(前提!$B$7,A14,-前提!$B$8,-前提!$B$2))</f>
         <v>424457.941200641</v>
       </c>
-      <c r="C14" s="17" t="str">
+      <c r="C14" s="18" t="str">
         <f aca="false">IF(スマホ!B39="","",スマホ!B39)</f>
         <v/>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="18" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A14&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A14-ボード!$B$4),FV(前提!$B$7,A14-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>417064.351948939</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="19" t="n">
+      <c r="A15" s="20" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="17" t="n">
+      <c r="B15" s="18" t="n">
         <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A15,FV(前提!$B$7,A15,-前提!$B$8,-前提!$B$2))</f>
         <v>457663.557938913</v>
       </c>
-      <c r="C15" s="17" t="str">
+      <c r="C15" s="18" t="str">
         <f aca="false">IF(スマホ!B40="","",スマホ!B40)</f>
         <v/>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="18" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A15&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A15-ボード!$B$4),FV(前提!$B$7,A15-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>450696.53819201</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="19" t="n">
+      <c r="A16" s="20" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="17" t="n">
+      <c r="B16" s="18" t="n">
         <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A16,FV(前提!$B$7,A16,-前提!$B$8,-前提!$B$2))</f>
         <v>490949.421584303</v>
       </c>
-      <c r="C16" s="17" t="str">
+      <c r="C16" s="18" t="str">
         <f aca="false">IF(スマホ!B41="","",スマホ!B41)</f>
         <v/>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="18" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A16&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A16-ボード!$B$4),FV(前提!$B$7,A16-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>484410.002218498</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="19" t="n">
+      <c r="A17" s="20" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="17" t="n">
+      <c r="B17" s="18" t="n">
         <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A17,FV(前提!$B$7,A17,-前提!$B$8,-前提!$B$2))</f>
         <v>524315.726066834</v>
       </c>
-      <c r="C17" s="17" t="str">
+      <c r="C17" s="18" t="str">
         <f aca="false">IF(スマホ!B42="","",スマホ!B42)</f>
         <v/>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="18" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A17&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A17-ボード!$B$4),FV(前提!$B$7,A17-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>518204.940449719</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="n">
+      <c r="A18" s="20" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="17" t="n">
+      <c r="B18" s="18" t="n">
         <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A18,FV(前提!$B$7,A18,-前提!$B$8,-前提!$B$2))</f>
         <v>557762.6657852</v>
       </c>
-      <c r="C18" s="17" t="str">
+      <c r="C18" s="18" t="str">
         <f aca="false">IF(スマホ!B43="","",スマホ!B43)</f>
         <v/>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D18" s="18" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A18&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A18-ボード!$B$4),FV(前提!$B$7,A18-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>552081.549781664</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19" t="n">
+      <c r="A19" s="20" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="17" t="n">
+      <c r="B19" s="18" t="n">
         <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A19,FV(前提!$B$7,A19,-前提!$B$8,-前提!$B$2))</f>
         <v>591290.435607884</v>
       </c>
-      <c r="C19" s="17" t="str">
+      <c r="C19" s="18" t="str">
         <f aca="false">IF(スマホ!B44="","",スマホ!B44)</f>
         <v/>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D19" s="18" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A19&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A19-ボード!$B$4),FV(前提!$B$7,A19-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>586040.027586163</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="19" t="n">
+      <c r="A20" s="20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="17" t="n">
+      <c r="B20" s="18" t="n">
         <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A20,FV(前提!$B$7,A20,-前提!$B$8,-前提!$B$2))</f>
         <v>624899.230874306</v>
       </c>
-      <c r="C20" s="17" t="str">
+      <c r="C20" s="18" t="str">
         <f aca="false">IF(スマホ!B45="","",スマホ!B45)</f>
         <v/>
       </c>
-      <c r="D20" s="17" t="n">
+      <c r="D20" s="18" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A20&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A20-ボード!$B$4),FV(前提!$B$7,A20-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>620080.571712022</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19" t="n">
+      <c r="A21" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="17" t="n">
+      <c r="B21" s="18" t="n">
         <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A21,FV(前提!$B$7,A21,-前提!$B$8,-前提!$B$2))</f>
         <v>658589.247395956</v>
       </c>
-      <c r="C21" s="17" t="str">
+      <c r="C21" s="18" t="str">
         <f aca="false">IF(スマホ!B46="","",スマホ!B46)</f>
         <v/>
       </c>
-      <c r="D21" s="17" t="n">
+      <c r="D21" s="18" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A21&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A21-ボード!$B$4),FV(前提!$B$7,A21-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>654203.380486184</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19" t="n">
+      <c r="A22" s="20" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="17" t="n">
+      <c r="B22" s="18" t="n">
         <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A22,FV(前提!$B$7,A22,-前提!$B$8,-前提!$B$2))</f>
         <v>692360.681457534</v>
       </c>
-      <c r="C22" s="17" t="str">
+      <c r="C22" s="18" t="str">
         <f aca="false">IF(スマホ!B47="","",スマホ!B47)</f>
         <v/>
       </c>
-      <c r="D22" s="17" t="n">
+      <c r="D22" s="18" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A22&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A22-ボード!$B$4),FV(前提!$B$7,A22-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>688408.652714886</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19" t="n">
+      <c r="A23" s="20" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="17" t="n">
+      <c r="B23" s="18" t="n">
         <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A23,FV(前提!$B$7,A23,-前提!$B$8,-前提!$B$2))</f>
         <v>726213.729818092</v>
       </c>
-      <c r="C23" s="17" t="str">
+      <c r="C23" s="18" t="str">
         <f aca="false">IF(スマホ!B48="","",スマホ!B48)</f>
         <v/>
       </c>
-      <c r="D23" s="17" t="n">
+      <c r="D23" s="18" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A23&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A23-ボード!$B$4),FV(前提!$B$7,A23-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>722696.587684805</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="n">
+      <c r="A24" s="20" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="17" t="n">
+      <c r="B24" s="18" t="n">
         <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A24,FV(前提!$B$7,A24,-前提!$B$8,-前提!$B$2))</f>
         <v>760148.589712189</v>
       </c>
-      <c r="C24" s="17" t="str">
+      <c r="C24" s="18" t="str">
         <f aca="false">IF(スマホ!B49="","",スマホ!B49)</f>
         <v/>
       </c>
-      <c r="D24" s="17" t="n">
+      <c r="D24" s="18" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A24&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A24-ボード!$B$4),FV(前提!$B$7,A24-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>757067.385164236</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="19" t="n">
+      <c r="A25" s="20" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="17" t="n">
+      <c r="B25" s="18" t="n">
         <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A25,FV(前提!$B$7,A25,-前提!$B$8,-前提!$B$2))</f>
         <v>794165.45885103</v>
       </c>
-      <c r="C25" s="17" t="str">
+      <c r="C25" s="18" t="str">
         <f aca="false">IF(スマホ!B50="","",スマホ!B50)</f>
         <v/>
       </c>
-      <c r="D25" s="17" t="n">
+      <c r="D25" s="18" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A25&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A25-ボード!$B$4),FV(前提!$B$7,A25-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>791521.245404242</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19" t="n">
+      <c r="A26" s="20" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="17" t="n">
+      <c r="B26" s="18" t="n">
         <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A26,FV(前提!$B$7,A26,-前提!$B$8,-前提!$B$2))</f>
         <v>828264.535423623</v>
       </c>
-      <c r="C26" s="17" t="str">
+      <c r="C26" s="18" t="str">
         <f aca="false">IF(スマホ!B51="","",スマホ!B51)</f>
         <v/>
       </c>
-      <c r="D26" s="17" t="n">
+      <c r="D26" s="18" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A26&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A26-ボード!$B$4),FV(前提!$B$7,A26-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>826058.369139829</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="n">
+      <c r="A27" s="20" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="17" t="n">
+      <c r="B27" s="18" t="n">
         <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A27,FV(前提!$B$7,A27,-前提!$B$8,-前提!$B$2))</f>
         <v>862446.018097934</v>
       </c>
-      <c r="C27" s="17" t="str">
+      <c r="C27" s="18" t="str">
         <f aca="false">IF(スマホ!B52="","",スマホ!B52)</f>
         <v/>
       </c>
-      <c r="D27" s="17" t="n">
+      <c r="D27" s="18" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A27&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A27-ボード!$B$4),FV(前提!$B$7,A27-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>860678.957591108</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="n">
+      <c r="A28" s="20" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="17" t="n">
+      <c r="B28" s="18" t="n">
         <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A28,FV(前提!$B$7,A28,-前提!$B$8,-前提!$B$2))</f>
         <v>896710.106022042</v>
       </c>
-      <c r="C28" s="17" t="str">
+      <c r="C28" s="18" t="str">
         <f aca="false">IF(スマホ!B53="","",スマホ!B53)</f>
         <v/>
       </c>
-      <c r="D28" s="17" t="n">
+      <c r="D28" s="18" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A28&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A28-ボード!$B$4),FV(前提!$B$7,A28-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>895383.212464479</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19" t="n">
+      <c r="A29" s="20" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="17" t="n">
+      <c r="B29" s="18" t="n">
         <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A29,FV(前提!$B$7,A29,-前提!$B$8,-前提!$B$2))</f>
         <v>931056.998825299</v>
       </c>
-      <c r="C29" s="17" t="str">
+      <c r="C29" s="18" t="str">
         <f aca="false">IF(スマホ!B54="","",スマホ!B54)</f>
         <v/>
       </c>
-      <c r="D29" s="17" t="n">
+      <c r="D29" s="18" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A29&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A29-ボード!$B$4),FV(前提!$B$7,A29-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>930171.335953793</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="19" t="n">
+      <c r="A30" s="20" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="17" t="n">
+      <c r="B30" s="18" t="n">
         <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A30,FV(前提!$B$7,A30,-前提!$B$8,-前提!$B$2))</f>
         <v>965486.896619496</v>
       </c>
-      <c r="C30" s="17" t="str">
+      <c r="C30" s="18" t="str">
         <f aca="false">IF(スマホ!B55="","",スマホ!B55)</f>
         <v/>
       </c>
-      <c r="D30" s="17" t="n">
+      <c r="D30" s="18" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A30&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A30-ボード!$B$4),FV(前提!$B$7,A30-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>965043.530741541</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="19" t="n">
+      <c r="A31" s="20" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="17" t="n">
+      <c r="B31" s="18" t="n">
         <f aca="false">IF(前提!$B$7=0,前提!$B$2+前提!$B$8*A31,FV(前提!$B$7,A31,-前提!$B$8,-前提!$B$2))</f>
         <v>1000000.00000003</v>
       </c>
-      <c r="C31" s="17" t="str">
+      <c r="C31" s="18" t="str">
         <f aca="false">IF(スマホ!B56="","",スマホ!B56)</f>
         <v/>
       </c>
-      <c r="D31" s="17" t="n">
+      <c r="D31" s="18" t="n">
         <f aca="false">IFERROR(IF(OR(ボード!$B$4="",ボード!$B$10="",A31&lt;=ボード!$B$4),"",IF(前提!$B$7=0,ボード!$B$5+ボード!$B$10*(A31-ボード!$B$4),FV(前提!$B$7,A31-ボード!$B$4,-ボード!$B$10,-ボード!$B$5))),"")</f>
         <v>1000000.00000003</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="11" t="s">
+      <c r="A33" s="12" t="s">
         <v>63</v>
       </c>
     </row>
@@ -4282,7 +4288,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>64</v>
       </c>
     </row>
@@ -4295,7 +4301,7 @@
       <c r="A4" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B4" s="19" t="n">
+      <c r="B4" s="20" t="n">
         <f aca="false">IF(COUNT(記録!C2:C31)=0,"",INDEX(記録!A2:A31,MATCH(9.99E+307,記録!C2:C31)))</f>
         <v>4</v>
       </c>
@@ -4304,7 +4310,7 @@
       <c r="A5" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B5" s="20" t="n">
+      <c r="B5" s="21" t="n">
         <f aca="false">IF(B4="","",INDEX(記録!C2:C31,MATCH(9.99E+307,記録!C2:C31)))</f>
         <v>118000</v>
       </c>
@@ -4313,7 +4319,7 @@
       <c r="A6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="18" t="n">
         <f aca="false">前提!B3</f>
         <v>1000000</v>
       </c>
@@ -4322,7 +4328,7 @@
       <c r="A7" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B7" s="21" t="n">
+      <c r="B7" s="22" t="n">
         <f aca="false">IF(OR(B4="",前提!B3=前提!B2),"",(B5-前提!B2)/(前提!B3-前提!B2))</f>
         <v>0.118</v>
       </c>
@@ -4331,7 +4337,7 @@
       <c r="A8" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B8" s="22" t="str">
+      <c r="B8" s="23" t="str">
         <f aca="false">IF(B4="","",IF(B5&gt;=INDEX(記録!B2:B31,B4),"計画どおり、または先行","計画より遅れ"))</f>
         <v>計画より遅れ</v>
       </c>
@@ -4340,7 +4346,7 @@
       <c r="A9" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="19" t="n">
+      <c r="B9" s="20" t="n">
         <f aca="false">IF(B4="","",前提!B4-B4)</f>
         <v>26</v>
       </c>
@@ -4349,7 +4355,7 @@
       <c r="A10" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B10" s="20" t="n">
+      <c r="B10" s="21" t="n">
         <f aca="false">IF(B4="","",IF(B5&gt;=前提!B3,0,IF(B9&lt;=0,"",IF(前提!B7=0,(前提!B3-B5)/B9,PMT(前提!B7,B9,B5,-前提!B3)))))</f>
         <v>32624.2807258581</v>
       </c>
@@ -4358,7 +4364,7 @@
       <c r="A11" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B11" s="17" t="n">
+      <c r="B11" s="18" t="n">
         <f aca="false">前提!B8</f>
         <v>32179.8433803691</v>
       </c>
@@ -4367,7 +4373,7 @@
       <c r="A12" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B12" s="20" t="n">
+      <c r="B12" s="21" t="n">
         <f aca="false">IF(B4="","",IF(B9&lt;=0,B5,IF(前提!B7=0,B5+前提!B8*B9,FV(前提!B7,B9,-前提!B8,-B5))))</f>
         <v>988088.717077351</v>
       </c>
@@ -4376,18 +4382,18 @@
       <c r="A13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="23" t="str">
+      <c r="B13" s="24" t="str">
         <f aca="false">IF(COUNTIF(記録!C2:C31,"&lt;0")&gt;0,"マイナスの値があります。確認してください",IF(B4="","実績を入力してください",IF(B9&lt;=0,"期限に達しました（前提の見直しが必要）",IF(COUNT(記録!C2:C31)&lt;B4,"入力していない月があります（現在地は最後に入力した月で計算）","OK"))))</f>
         <v>OK</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="12" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="12" t="s">
         <v>76</v>
       </c>
     </row>
